--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/18-resultado-mensal.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/18-resultado-mensal.xlsx
@@ -472,7 +472,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Resultado'!A12</f>
+              <f>'Resultado'!A11</f>
             </strRef>
           </tx>
           <spPr>
@@ -493,7 +493,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Resultado'!$B$12:$M$12</f>
+              <f>'Resultado'!$B$11:$M$11</f>
             </numRef>
           </val>
         </ser>
@@ -502,7 +502,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Resultado'!A34</f>
+              <f>'Resultado'!A35</f>
             </strRef>
           </tx>
           <spPr>
@@ -523,7 +523,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Resultado'!$B$34:$M$34</f>
+              <f>'Resultado'!$B$35:$M$35</f>
             </numRef>
           </val>
         </ser>
@@ -532,7 +532,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Resultado'!A35</f>
+              <f>'Resultado'!A36</f>
             </strRef>
           </tx>
           <spPr>
@@ -553,7 +553,7 @@
           </cat>
           <val>
             <numRef>
-              <f>'Resultado'!$B$35:$M$35</f>
+              <f>'Resultado'!$B$36:$M$36</f>
             </numRef>
           </val>
         </ser>
@@ -938,7 +938,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Uma DRE simplificada da clínica: receita por categoria (as mesmas do caixa), custos fixos, despesas variáveis (materiais, taxas de cartão, repasse à parceira, manutenção), pró-labore fixo, impostos provisionados como % da receita, resultado e margem, mês a mês. Compara o mês com o anterior e com o que você previu.</t>
+          <t>Uma DRE simplificada da clínica: receita por categoria (as mesmas do caixa), custos fixos, despesas variáveis (materiais, taxas de cartão, repasse à parceira, manutenção), pró-labore fixo, a provisão de 13º e férias (planilha 10) e os impostos provisionados como % da receita, resultado e margem, mês a mês. Compara o mês com o anterior e com o que você previu. Reembolso de sócio fica fora da receita e fora do imposto.</t>
         </is>
       </c>
     </row>
@@ -962,7 +962,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Em Resultado, preencha por mês o que entrou em cada categoria e o que saiu em cada linha de custo fixo, despesa variável e pró-labore. Os totais por categoria estão no Painel da planilha 09 · Caixa da clínica ("De onde veio" e "Para onde foi o dinheiro").</t>
+          <t>Em Resultado, preencha por mês o que entrou em cada categoria de receita e o que saiu em cada linha de custo fixo, despesa variável e pró-labore. Os totais por categoria estão no Painel da planilha 09 · Caixa da clínica ("De onde veio" e "Para onde foi o dinheiro"). Reembolso de sócio vai na linha própria, fora da receita. A provisão de 13º e férias você copia do Painel da planilha 10.</t>
         </is>
       </c>
     </row>
@@ -1165,23 +1165,23 @@
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13">
-        <f>IF(INDEX(Resultado!$B$12:$M$12,Config!$B$8)="","—",INDEX(Resultado!$B$12:$M$12,Config!$B$8))</f>
-        <v>50336</v>
+        <f>IF(INDEX(Resultado!$B$11:$M$11,Config!$B$8)="","—",INDEX(Resultado!$B$11:$M$11,Config!$B$8))</f>
+        <v>49651</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="13">
-        <f>IF(INDEX(Resultado!$B$34:$M$34,Config!$B$8)="","—",INDEX(Resultado!$B$34:$M$34,Config!$B$8))</f>
-        <v>40696.12</v>
+        <f>IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8))</f>
+        <v>42583.12</v>
       </c>
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="14">
-        <f>IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8))</f>
-        <v>9639.88000000001</v>
+        <f>IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8))</f>
+        <v>7067.88000000001</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="15">
-        <f>IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8))</f>
-        <v>0.191510648442467</v>
+        <f>IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8))</f>
+        <v>0.142351211455963</v>
       </c>
       <c r="H5" s="12" t="n"/>
     </row>
@@ -1239,16 +1239,16 @@
       </c>
       <c r="B9" s="18" t="n"/>
       <c r="C9" s="20">
-        <f>IF(INDEX(Resultado!$B$12:$M$12,Config!$B$8)="","—",INDEX(Resultado!$B$12:$M$12,Config!$B$8))</f>
-        <v>50336</v>
+        <f>IF(INDEX(Resultado!$B$11:$M$11,Config!$B$8)="","—",INDEX(Resultado!$B$11:$M$11,Config!$B$8))</f>
+        <v>49651</v>
       </c>
       <c r="D9" s="20">
-        <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$12:$M$12,Config!$B$8-1)="","—",INDEX(Resultado!$B$12:$M$12,Config!$B$8-1)))</f>
-        <v>53101</v>
+        <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$11:$M$11,Config!$B$8-1)="","—",INDEX(Resultado!$B$11:$M$11,Config!$B$8-1)))</f>
+        <v>53461</v>
       </c>
       <c r="E9" s="21">
         <f>IF(OR(C9="—",D9="—",D9=0),"—",(C9-D9)/ABS(D9))</f>
-        <v>-0.0520705824749063</v>
+        <v>-0.0712669048465236</v>
       </c>
       <c r="F9" s="20">
         <f>IF(INDEX(Previsto!$B$5:$M$5,Config!$B$8)="","—",INDEX(Previsto!$B$5:$M$5,Config!$B$8))</f>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G9" s="21">
         <f>IF(OR(C9="—",F9="—",F9=0),"—",(C9-F9)/ABS(F9))</f>
-        <v>0.0942608695652174</v>
+        <v>0.0793695652173913</v>
       </c>
       <c r="H9" s="22" t="str">
         <f>IF(OR(C9="—",F9="—"),"—",IF(C9&gt;=F9,"Dentro do previsto",IF(C9&gt;=F9*0.95,"Perto","Fora do previsto")))</f>
@@ -1363,29 +1363,29 @@
     <row r="13">
       <c r="A13" s="23" t="inlineStr">
         <is>
-          <t>Impostos provisionados</t>
+          <t>Provisão de 13º e férias</t>
         </is>
       </c>
       <c r="B13" s="18" t="n"/>
       <c r="C13" s="20">
         <f>IF(INDEX(Resultado!$B$33:$M$33,Config!$B$8)="","—",INDEX(Resultado!$B$33:$M$33,Config!$B$8))</f>
-        <v>5537</v>
+        <v>1962</v>
       </c>
       <c r="D13" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$33:$M$33,Config!$B$8-1)="","—",INDEX(Resultado!$B$33:$M$33,Config!$B$8-1)))</f>
-        <v>5841</v>
+        <v>1962</v>
       </c>
       <c r="E13" s="21">
         <f>IF(OR(C13="—",D13="—",D13=0),"—",(C13-D13)/ABS(D13))</f>
-        <v>-0.0520458825543571</v>
+        <v>0</v>
       </c>
       <c r="F13" s="20">
         <f>IF(INDEX(Previsto!$B$9:$M$9,Config!$B$8)="","—",INDEX(Previsto!$B$9:$M$9,Config!$B$8))</f>
-        <v>5060</v>
+        <v>1962</v>
       </c>
       <c r="G13" s="21">
         <f>IF(OR(C13="—",F13="—",F13=0),"—",(C13-F13)/ABS(F13))</f>
-        <v>0.0942687747035573</v>
+        <v>0</v>
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
@@ -1394,279 +1394,288 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>Total de saídas</t>
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Impostos provisionados</t>
         </is>
       </c>
       <c r="B14" s="18" t="n"/>
       <c r="C14" s="20">
         <f>IF(INDEX(Resultado!$B$34:$M$34,Config!$B$8)="","—",INDEX(Resultado!$B$34:$M$34,Config!$B$8))</f>
-        <v>40696.12</v>
+        <v>5462</v>
       </c>
       <c r="D14" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$34:$M$34,Config!$B$8-1)="","—",INDEX(Resultado!$B$34:$M$34,Config!$B$8-1)))</f>
-        <v>40502.77</v>
+        <v>5881</v>
       </c>
       <c r="E14" s="21">
         <f>IF(OR(C14="—",D14="—",D14=0),"—",(C14-D14)/ABS(D14))</f>
-        <v>0.00477374757331391</v>
+        <v>-0.0712463866689339</v>
       </c>
       <c r="F14" s="20">
         <f>IF(INDEX(Previsto!$B$10:$M$10,Config!$B$8)="","—",INDEX(Previsto!$B$10:$M$10,Config!$B$8))</f>
-        <v>39060</v>
+        <v>5060</v>
       </c>
       <c r="G14" s="21">
         <f>IF(OR(C14="—",F14="—",F14=0),"—",(C14-F14)/ABS(F14))</f>
-        <v>0.0418873527905785</v>
-      </c>
-      <c r="H14" s="22" t="str">
-        <f>IF(OR(C14="—",F14="—"),"—",IF(C14&lt;=F14,"Dentro do previsto",IF(C14&lt;=F14*1.05,"Perto","Fora do previsto")))</f>
-        <v>Perto</v>
+        <v>0.0794466403162055</v>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t>Informativo</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>Resultado do mês</t>
+          <t>Total de saídas</t>
         </is>
       </c>
       <c r="B15" s="18" t="n"/>
       <c r="C15" s="20">
         <f>IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8))</f>
-        <v>9639.88000000001</v>
+        <v>42583.12</v>
       </c>
       <c r="D15" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8-1)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8-1)))</f>
-        <v>12598.23</v>
+        <v>42504.77</v>
       </c>
       <c r="E15" s="21">
         <f>IF(OR(C15="—",D15="—",D15=0),"—",(C15-D15)/ABS(D15))</f>
-        <v>-0.234822669533735</v>
+        <v>0.00184332252591865</v>
       </c>
       <c r="F15" s="20">
         <f>IF(INDEX(Previsto!$B$11:$M$11,Config!$B$8)="","—",INDEX(Previsto!$B$11:$M$11,Config!$B$8))</f>
-        <v>6940</v>
+        <v>41022</v>
       </c>
       <c r="G15" s="21">
         <f>IF(OR(C15="—",F15="—",F15=0),"—",(C15-F15)/ABS(F15))</f>
-        <v>0.389031700288185</v>
+        <v>0.0380556774413728</v>
       </c>
       <c r="H15" s="22" t="str">
-        <f>IF(OR(C15="—",F15="—"),"—",IF(C15&gt;=F15,"Dentro do previsto",IF(C15&gt;=F15*0.95,"Perto","Fora do previsto")))</f>
-        <v>Dentro do previsto</v>
+        <f>IF(OR(C15="—",F15="—"),"—",IF(C15&lt;=F15,"Dentro do previsto",IF(C15&lt;=F15*1.05,"Perto","Fora do previsto")))</f>
+        <v>Perto</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
-        <is>
-          <t>Margem</t>
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>Resultado do mês</t>
         </is>
       </c>
       <c r="B16" s="18" t="n"/>
-      <c r="C16" s="24">
+      <c r="C16" s="20">
         <f>IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8))</f>
-        <v>0.191510648442467</v>
-      </c>
-      <c r="D16" s="24">
+        <v>7067.88000000001</v>
+      </c>
+      <c r="D16" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8-1)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8-1)))</f>
-        <v>0.237250334268658</v>
-      </c>
-      <c r="E16" s="25">
-        <f>IF(OR(C16="—",D16="—"),"—",(C16-D16)*100)</f>
-        <v>-4.57396858261911</v>
-      </c>
-      <c r="F16" s="24">
+        <v>10956.23</v>
+      </c>
+      <c r="E16" s="21">
+        <f>IF(OR(C16="—",D16="—",D16=0),"—",(C16-D16)/ABS(D16))</f>
+        <v>-0.354898537179303</v>
+      </c>
+      <c r="F16" s="20">
         <f>IF(INDEX(Previsto!$B$12:$M$12,Config!$B$8)="","—",INDEX(Previsto!$B$12:$M$12,Config!$B$8))</f>
-        <v>0.150869565217391</v>
-      </c>
-      <c r="G16" s="25">
-        <f>IF(OR(C16="—",F16="—"),"—",(C16-F16)*100)</f>
-        <v>4.06410832250754</v>
+        <v>4978</v>
+      </c>
+      <c r="G16" s="21">
+        <f>IF(OR(C16="—",F16="—",F16=0),"—",(C16-F16)/ABS(F16))</f>
+        <v>0.419823222177582</v>
       </c>
       <c r="H16" s="22" t="str">
         <f>IF(OR(C16="—",F16="—"),"—",IF(C16&gt;=F16,"Dentro do previsto",IF(C16&gt;=F16*0.95,"Perto","Fora do previsto")))</f>
         <v>Dentro do previsto</v>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Margem</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="24">
+        <f>IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8))</f>
+        <v>0.142351211455963</v>
+      </c>
+      <c r="D17" s="24">
+        <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8-1)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8-1)))</f>
+        <v>0.204938740390191</v>
+      </c>
+      <c r="E17" s="25">
+        <f>IF(OR(C17="—",D17="—"),"—",(C17-D17)*100)</f>
+        <v>-6.25875289342282</v>
+      </c>
+      <c r="F17" s="24">
+        <f>IF(INDEX(Previsto!$B$13:$M$13,Config!$B$8)="","—",INDEX(Previsto!$B$13:$M$13,Config!$B$8))</f>
+        <v>0.108217391304348</v>
+      </c>
+      <c r="G17" s="25">
+        <f>IF(OR(C17="—",F17="—"),"—",(C17-F17)*100)</f>
+        <v>3.41338201516149</v>
+      </c>
+      <c r="H17" s="22" t="str">
+        <f>IF(OR(C17="—",F17="—"),"—",IF(C17&gt;=F17,"Dentro do previsto",IF(C17&gt;=F17*0.95,"Perto","Fora do previsto")))</f>
+        <v>Dentro do previsto</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Receita do mês por categoria</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="B19" s="18" t="n"/>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="17" t="inlineStr">
         <is>
           <t>Mês</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
         <is>
           <t>Mês anterior</t>
         </is>
       </c>
-      <c r="E19" s="17" t="inlineStr">
+      <c r="E20" s="17" t="inlineStr">
         <is>
           <t>Variação</t>
         </is>
       </c>
-      <c r="F19" s="17" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>% da receita</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
         <is>
           <t>Particular à vista</t>
         </is>
       </c>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="20">
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="20">
         <f>IF(INDEX(Resultado!$B$6:$M$6,Config!$B$8)="","—",INDEX(Resultado!$B$6:$M$6,Config!$B$8))</f>
         <v>33860</v>
       </c>
-      <c r="D20" s="20">
+      <c r="D21" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$6:$M$6,Config!$B$8-1)="","—",INDEX(Resultado!$B$6:$M$6,Config!$B$8-1)))</f>
-        <v>36540</v>
-      </c>
-      <c r="E20" s="21">
-        <f>IF(OR(C20="—",D20="—",D20=0),"—",(C20-D20)/ABS(D20))</f>
-        <v>-0.073344280240832</v>
-      </c>
-      <c r="F20" s="26">
-        <f>IF(OR(C20="—",C9="—",C9=0),"—",C20/C9)</f>
-        <v>0.672679593134139</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>Particular a prazo</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="n"/>
-      <c r="C21" s="20">
-        <f>IF(INDEX(Resultado!$B$7:$M$7,Config!$B$8)="","—",INDEX(Resultado!$B$7:$M$7,Config!$B$8))</f>
-        <v>5315</v>
-      </c>
-      <c r="D21" s="20">
-        <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$7:$M$7,Config!$B$8-1)="","—",INDEX(Resultado!$B$7:$M$7,Config!$B$8-1)))</f>
-        <v>6760</v>
+        <v>37700</v>
       </c>
       <c r="E21" s="21">
         <f>IF(OR(C21="—",D21="—",D21=0),"—",(C21-D21)/ABS(D21))</f>
-        <v>-0.213757396449704</v>
+        <v>-0.101856763925729</v>
       </c>
       <c r="F21" s="26">
         <f>IF(OR(C21="—",C9="—",C9=0),"—",C21/C9)</f>
-        <v>0.105590432294978</v>
+        <v>0.681960081367948</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>Convênio · Saúde Total</t>
+          <t>Particular a prazo</t>
         </is>
       </c>
       <c r="B22" s="18" t="n"/>
       <c r="C22" s="20">
+        <f>IF(INDEX(Resultado!$B$7:$M$7,Config!$B$8)="","—",INDEX(Resultado!$B$7:$M$7,Config!$B$8))</f>
+        <v>4630</v>
+      </c>
+      <c r="D22" s="20">
+        <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$7:$M$7,Config!$B$8-1)="","—",INDEX(Resultado!$B$7:$M$7,Config!$B$8-1)))</f>
+        <v>5960</v>
+      </c>
+      <c r="E22" s="21">
+        <f>IF(OR(C22="—",D22="—",D22=0),"—",(C22-D22)/ABS(D22))</f>
+        <v>-0.223154362416107</v>
+      </c>
+      <c r="F22" s="26">
+        <f>IF(OR(C22="—",C9="—",C9=0),"—",C22/C9)</f>
+        <v>0.0932508912207206</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Convênio · Saúde Total</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="20">
         <f>IF(INDEX(Resultado!$B$8:$M$8,Config!$B$8)="","—",INDEX(Resultado!$B$8:$M$8,Config!$B$8))</f>
         <v>7320</v>
       </c>
-      <c r="D22" s="20">
+      <c r="D23" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$8:$M$8,Config!$B$8-1)="","—",INDEX(Resultado!$B$8:$M$8,Config!$B$8-1)))</f>
         <v>6655</v>
       </c>
-      <c r="E22" s="21">
-        <f>IF(OR(C22="—",D22="—",D22=0),"—",(C22-D22)/ABS(D22))</f>
+      <c r="E23" s="21">
+        <f>IF(OR(C23="—",D23="—",D23=0),"—",(C23-D23)/ABS(D23))</f>
         <v>0.0999248685199098</v>
       </c>
-      <c r="F22" s="26">
-        <f>IF(OR(C22="—",C9="—",C9=0),"—",C22/C9)</f>
-        <v>0.145422759059123</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="F23" s="26">
+        <f>IF(OR(C23="—",C9="—",C9=0),"—",C23/C9)</f>
+        <v>0.147429054802522</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>Convênio · MediPlan</t>
         </is>
       </c>
-      <c r="B23" s="18" t="n"/>
-      <c r="C23" s="20">
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="20">
         <f>IF(INDEX(Resultado!$B$9:$M$9,Config!$B$8)="","—",INDEX(Resultado!$B$9:$M$9,Config!$B$8))</f>
         <v>2130</v>
       </c>
-      <c r="D23" s="20">
+      <c r="D24" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$9:$M$9,Config!$B$8-1)="","—",INDEX(Resultado!$B$9:$M$9,Config!$B$8-1)))</f>
         <v>1570</v>
       </c>
-      <c r="E23" s="21">
-        <f>IF(OR(C23="—",D23="—",D23=0),"—",(C23-D23)/ABS(D23))</f>
+      <c r="E24" s="21">
+        <f>IF(OR(C24="—",D24="—",D24=0),"—",(C24-D24)/ABS(D24))</f>
         <v>0.356687898089172</v>
       </c>
-      <c r="F23" s="26">
-        <f>IF(OR(C23="—",C9="—",C9=0),"—",C23/C9)</f>
-        <v>0.042315638906548</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="F24" s="26">
+        <f>IF(OR(C24="—",C9="—",C9=0),"—",C24/C9)</f>
+        <v>0.0428994380777829</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>Convênio · Vida Care</t>
         </is>
       </c>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="20">
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="20">
         <f>IF(INDEX(Resultado!$B$10:$M$10,Config!$B$8)="","—",INDEX(Resultado!$B$10:$M$10,Config!$B$8))</f>
         <v>1711</v>
       </c>
-      <c r="D24" s="20">
+      <c r="D25" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$10:$M$10,Config!$B$8-1)="","—",INDEX(Resultado!$B$10:$M$10,Config!$B$8-1)))</f>
         <v>1576</v>
       </c>
-      <c r="E24" s="21">
-        <f>IF(OR(C24="—",D24="—",D24=0),"—",(C24-D24)/ABS(D24))</f>
+      <c r="E25" s="21">
+        <f>IF(OR(C25="—",D25="—",D25=0),"—",(C25-D25)/ABS(D25))</f>
         <v>0.0856598984771574</v>
-      </c>
-      <c r="F24" s="26">
-        <f>IF(OR(C24="—",C9="—",C9=0),"—",C24/C9)</f>
-        <v>0.033991576605213</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>Outras entradas</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="20">
-        <f>IF(INDEX(Resultado!$B$11:$M$11,Config!$B$8)="","—",INDEX(Resultado!$B$11:$M$11,Config!$B$8))</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="20">
-        <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$11:$M$11,Config!$B$8-1)="","—",INDEX(Resultado!$B$11:$M$11,Config!$B$8-1)))</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="21" t="str">
-        <f>IF(OR(C25="—",D25="—",D25=0),"—",(C25-D25)/ABS(D25))</f>
-        <v>—</v>
       </c>
       <c r="F25" s="26">
         <f>IF(OR(C25="—",C9="—",C9=0),"—",C25/C9)</f>
-        <v>0</v>
+        <v>0.0344605345310266</v>
       </c>
     </row>
     <row r="26"/>
@@ -1711,6 +1720,7 @@
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="A16:B16"/>
@@ -1723,14 +1733,13 @@
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A18:J18"/>
     <mergeCell ref="A27:J27"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A13:B13"/>
@@ -1741,7 +1750,7 @@
       <formula>AND(ISNUMBER(E5),E5&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H9:H16">
+  <conditionalFormatting sqref="H9:H17">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>H9="Dentro do previsto"</formula>
     </cfRule>
@@ -1962,7 +1971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -2107,19 +2116,19 @@
         <v>15870</v>
       </c>
       <c r="D6" s="35" t="n">
-        <v>37340</v>
+        <v>37790</v>
       </c>
       <c r="E6" s="35" t="n">
         <v>28610</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>27400</v>
+        <v>27800</v>
       </c>
       <c r="G6" s="35" t="n">
-        <v>27400</v>
+        <v>28560</v>
       </c>
       <c r="H6" s="35" t="n">
-        <v>36540</v>
+        <v>37700</v>
       </c>
       <c r="I6" s="35" t="n">
         <v>33860</v>
@@ -2130,11 +2139,11 @@
       <c r="M6" s="35" t="n"/>
       <c r="N6" s="20">
         <f>IF(COUNT(B6:M6)=0,"",SUM(B6:M6))</f>
-        <v>232200</v>
+        <v>235370</v>
       </c>
       <c r="O6" s="20">
         <f>IF(COUNT(B6:M6)=0,"",AVERAGE(B6:M6))</f>
-        <v>29025</v>
+        <v>29421.25</v>
       </c>
     </row>
     <row r="7">
@@ -2153,19 +2162,19 @@
         <v>3990</v>
       </c>
       <c r="E7" s="35" t="n">
-        <v>4195</v>
+        <v>4160</v>
       </c>
       <c r="F7" s="35" t="n">
-        <v>6280</v>
+        <v>5865</v>
       </c>
       <c r="G7" s="35" t="n">
-        <v>8680</v>
+        <v>7825</v>
       </c>
       <c r="H7" s="35" t="n">
-        <v>6760</v>
+        <v>5960</v>
       </c>
       <c r="I7" s="35" t="n">
-        <v>5315</v>
+        <v>4630</v>
       </c>
       <c r="J7" s="35" t="n"/>
       <c r="K7" s="35" t="n"/>
@@ -2173,11 +2182,11 @@
       <c r="M7" s="35" t="n"/>
       <c r="N7" s="20">
         <f>IF(COUNT(B7:M7)=0,"",SUM(B7:M7))</f>
-        <v>37045</v>
+        <v>34255</v>
       </c>
       <c r="O7" s="20">
         <f>IF(COUNT(B7:M7)=0,"",AVERAGE(B7:M7))</f>
-        <v>4630.625</v>
+        <v>4281.875</v>
       </c>
     </row>
     <row r="8">
@@ -2310,109 +2319,109 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Outras entradas</t>
-        </is>
-      </c>
-      <c r="B11" s="35" t="n">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>Receita total</t>
+        </is>
+      </c>
+      <c r="B11" s="36">
+        <f>IF(COUNT(B$6:B$10,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B6:B10))</f>
+        <v>33270</v>
+      </c>
+      <c r="C11" s="36">
+        <f>IF(COUNT(C$6:C$10,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C6:C10))</f>
+        <v>24795</v>
+      </c>
+      <c r="D11" s="36">
+        <f>IF(COUNT(D$6:D$10,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D6:D10))</f>
+        <v>48330</v>
+      </c>
+      <c r="E11" s="36">
+        <f>IF(COUNT(E$6:E$10,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E6:E10))</f>
+        <v>38935</v>
+      </c>
+      <c r="F11" s="36">
+        <f>IF(COUNT(F$6:F$10,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F6:F10))</f>
+        <v>44745</v>
+      </c>
+      <c r="G11" s="36">
+        <f>IF(COUNT(G$6:G$10,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G6:G10))</f>
+        <v>44160</v>
+      </c>
+      <c r="H11" s="36">
+        <f>IF(COUNT(H$6:H$10,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H6:H10))</f>
+        <v>53461</v>
+      </c>
+      <c r="I11" s="36">
+        <f>IF(COUNT(I$6:I$10,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I6:I10))</f>
+        <v>49651</v>
+      </c>
+      <c r="J11" s="36">
+        <f>IF(COUNT(J$6:J$10,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J6:J10))</f>
+        <v/>
+      </c>
+      <c r="K11" s="36">
+        <f>IF(COUNT(K$6:K$10,K$14:K$21,K$24:K$27,K$30:K$31)=0,"",SUM(K6:K10))</f>
+        <v/>
+      </c>
+      <c r="L11" s="36">
+        <f>IF(COUNT(L$6:L$10,L$14:L$21,L$24:L$27,L$30:L$31)=0,"",SUM(L6:L10))</f>
+        <v/>
+      </c>
+      <c r="M11" s="36">
+        <f>IF(COUNT(M$6:M$10,M$14:M$21,M$24:M$27,M$30:M$31)=0,"",SUM(M6:M10))</f>
+        <v/>
+      </c>
+      <c r="N11" s="36">
+        <f>IF(COUNT(B11:M11)=0,"",SUM(B11:M11))</f>
+        <v>337347</v>
+      </c>
+      <c r="O11" s="36">
+        <f>IF(COUNT(B11:M11)=0,"",AVERAGE(B11:M11))</f>
+        <v>42168.375</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Reembolsos de sócios (não é receita, não paga imposto)</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E12" s="35" t="n">
         <v>620</v>
       </c>
-      <c r="F11" s="35" t="n">
+      <c r="F12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="35" t="n">
+      <c r="G12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="35" t="n">
+      <c r="H12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="35" t="n">
+      <c r="I12" s="35" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="35" t="n"/>
-      <c r="K11" s="35" t="n"/>
-      <c r="L11" s="35" t="n"/>
-      <c r="M11" s="35" t="n"/>
-      <c r="N11" s="20">
-        <f>IF(COUNT(B11:M11)=0,"",SUM(B11:M11))</f>
+      <c r="J12" s="35" t="n"/>
+      <c r="K12" s="35" t="n"/>
+      <c r="L12" s="35" t="n"/>
+      <c r="M12" s="35" t="n"/>
+      <c r="N12" s="20">
+        <f>IF(COUNT(B12:M12)=0,"",SUM(B12:M12))</f>
         <v>620</v>
       </c>
-      <c r="O11" s="20">
-        <f>IF(COUNT(B11:M11)=0,"",AVERAGE(B11:M11))</f>
+      <c r="O12" s="20">
+        <f>IF(COUNT(B12:M12)=0,"",AVERAGE(B12:M12))</f>
         <v>77.5</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Receita total</t>
-        </is>
-      </c>
-      <c r="B12" s="36">
-        <f>IF(COUNT(B$6:B$11,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B6:B11))</f>
-        <v>33270</v>
-      </c>
-      <c r="C12" s="36">
-        <f>IF(COUNT(C$6:C$11,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C6:C11))</f>
-        <v>24795</v>
-      </c>
-      <c r="D12" s="36">
-        <f>IF(COUNT(D$6:D$11,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D6:D11))</f>
-        <v>47880</v>
-      </c>
-      <c r="E12" s="36">
-        <f>IF(COUNT(E$6:E$11,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E6:E11))</f>
-        <v>39590</v>
-      </c>
-      <c r="F12" s="36">
-        <f>IF(COUNT(F$6:F$11,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F6:F11))</f>
-        <v>44760</v>
-      </c>
-      <c r="G12" s="36">
-        <f>IF(COUNT(G$6:G$11,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G6:G11))</f>
-        <v>43855</v>
-      </c>
-      <c r="H12" s="36">
-        <f>IF(COUNT(H$6:H$11,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H6:H11))</f>
-        <v>53101</v>
-      </c>
-      <c r="I12" s="36">
-        <f>IF(COUNT(I$6:I$11,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I6:I11))</f>
-        <v>50336</v>
-      </c>
-      <c r="J12" s="36">
-        <f>IF(COUNT(J$6:J$11,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J6:J11))</f>
-        <v/>
-      </c>
-      <c r="K12" s="36">
-        <f>IF(COUNT(K$6:K$11,K$14:K$21,K$24:K$27,K$30:K$31)=0,"",SUM(K6:K11))</f>
-        <v/>
-      </c>
-      <c r="L12" s="36">
-        <f>IF(COUNT(L$6:L$11,L$14:L$21,L$24:L$27,L$30:L$31)=0,"",SUM(L6:L11))</f>
-        <v/>
-      </c>
-      <c r="M12" s="36">
-        <f>IF(COUNT(M$6:M$11,M$14:M$21,M$24:M$27,M$30:M$31)=0,"",SUM(M6:M11))</f>
-        <v/>
-      </c>
-      <c r="N12" s="36">
-        <f>IF(COUNT(B12:M12)=0,"",SUM(B12:M12))</f>
-        <v>337587</v>
-      </c>
-      <c r="O12" s="36">
-        <f>IF(COUNT(B12:M12)=0,"",AVERAGE(B12:M12))</f>
-        <v>42198.375</v>
       </c>
     </row>
     <row r="13">
@@ -2787,51 +2796,51 @@
         </is>
       </c>
       <c r="B22" s="36">
-        <f>IF(COUNT(B$6:B$11,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B14:B21))</f>
+        <f>IF(COUNT(B$6:B$10,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B14:B21))</f>
         <v>10000</v>
       </c>
       <c r="C22" s="36">
-        <f>IF(COUNT(C$6:C$11,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C14:C21))</f>
+        <f>IF(COUNT(C$6:C$10,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C14:C21))</f>
         <v>10000</v>
       </c>
       <c r="D22" s="36">
-        <f>IF(COUNT(D$6:D$11,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D14:D21))</f>
+        <f>IF(COUNT(D$6:D$10,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D14:D21))</f>
         <v>10000</v>
       </c>
       <c r="E22" s="36">
-        <f>IF(COUNT(E$6:E$11,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E14:E21))</f>
+        <f>IF(COUNT(E$6:E$10,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E14:E21))</f>
         <v>10000</v>
       </c>
       <c r="F22" s="36">
-        <f>IF(COUNT(F$6:F$11,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F14:F21))</f>
+        <f>IF(COUNT(F$6:F$10,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F14:F21))</f>
         <v>10000</v>
       </c>
       <c r="G22" s="36">
-        <f>IF(COUNT(G$6:G$11,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G14:G21))</f>
+        <f>IF(COUNT(G$6:G$10,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G14:G21))</f>
         <v>10000</v>
       </c>
       <c r="H22" s="36">
-        <f>IF(COUNT(H$6:H$11,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H14:H21))</f>
+        <f>IF(COUNT(H$6:H$10,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H14:H21))</f>
         <v>10000</v>
       </c>
       <c r="I22" s="36">
-        <f>IF(COUNT(I$6:I$11,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I14:I21))</f>
+        <f>IF(COUNT(I$6:I$10,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I14:I21))</f>
         <v>10000</v>
       </c>
       <c r="J22" s="36">
-        <f>IF(COUNT(J$6:J$11,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J14:J21))</f>
+        <f>IF(COUNT(J$6:J$10,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J14:J21))</f>
         <v/>
       </c>
       <c r="K22" s="36">
-        <f>IF(COUNT(K$6:K$11,K$14:K$21,K$24:K$27,K$30:K$31)=0,"",SUM(K14:K21))</f>
+        <f>IF(COUNT(K$6:K$10,K$14:K$21,K$24:K$27,K$30:K$31)=0,"",SUM(K14:K21))</f>
         <v/>
       </c>
       <c r="L22" s="36">
-        <f>IF(COUNT(L$6:L$11,L$14:L$21,L$24:L$27,L$30:L$31)=0,"",SUM(L14:L21))</f>
+        <f>IF(COUNT(L$6:L$10,L$14:L$21,L$24:L$27,L$30:L$31)=0,"",SUM(L14:L21))</f>
         <v/>
       </c>
       <c r="M22" s="36">
-        <f>IF(COUNT(M$6:M$11,M$14:M$21,M$24:M$27,M$30:M$31)=0,"",SUM(M14:M21))</f>
+        <f>IF(COUNT(M$6:M$10,M$14:M$21,M$24:M$27,M$30:M$31)=0,"",SUM(M14:M21))</f>
         <v/>
       </c>
       <c r="N22" s="36">
@@ -3043,51 +3052,51 @@
         </is>
       </c>
       <c r="B28" s="36">
-        <f>IF(COUNT(B$6:B$11,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B24:B27))</f>
+        <f>IF(COUNT(B$6:B$10,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B24:B27))</f>
         <v>4570.56</v>
       </c>
       <c r="C28" s="36">
-        <f>IF(COUNT(C$6:C$11,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C24:C27))</f>
+        <f>IF(COUNT(C$6:C$10,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C24:C27))</f>
         <v>4810.28</v>
       </c>
       <c r="D28" s="36">
-        <f>IF(COUNT(D$6:D$11,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D24:D27))</f>
+        <f>IF(COUNT(D$6:D$10,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D24:D27))</f>
         <v>5338.25</v>
       </c>
       <c r="E28" s="36">
-        <f>IF(COUNT(E$6:E$11,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E24:E27))</f>
+        <f>IF(COUNT(E$6:E$10,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E24:E27))</f>
         <v>7745.7</v>
       </c>
       <c r="F28" s="36">
-        <f>IF(COUNT(F$6:F$11,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F24:F27))</f>
+        <f>IF(COUNT(F$6:F$10,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F24:F27))</f>
         <v>7069.12</v>
       </c>
       <c r="G28" s="36">
-        <f>IF(COUNT(G$6:G$11,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G24:G27))</f>
+        <f>IF(COUNT(G$6:G$10,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G24:G27))</f>
         <v>7109.91</v>
       </c>
       <c r="H28" s="36">
-        <f>IF(COUNT(H$6:H$11,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H24:H27))</f>
+        <f>IF(COUNT(H$6:H$10,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H24:H27))</f>
         <v>6661.77</v>
       </c>
       <c r="I28" s="36">
-        <f>IF(COUNT(I$6:I$11,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I24:I27))</f>
+        <f>IF(COUNT(I$6:I$10,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I24:I27))</f>
         <v>7159.12</v>
       </c>
       <c r="J28" s="36">
-        <f>IF(COUNT(J$6:J$11,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J24:J27))</f>
+        <f>IF(COUNT(J$6:J$10,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J24:J27))</f>
         <v/>
       </c>
       <c r="K28" s="36">
-        <f>IF(COUNT(K$6:K$11,K$14:K$21,K$24:K$27,K$30:K$31)=0,"",SUM(K24:K27))</f>
+        <f>IF(COUNT(K$6:K$10,K$14:K$21,K$24:K$27,K$30:K$31)=0,"",SUM(K24:K27))</f>
         <v/>
       </c>
       <c r="L28" s="36">
-        <f>IF(COUNT(L$6:L$11,L$14:L$21,L$24:L$27,L$30:L$31)=0,"",SUM(L24:L27))</f>
+        <f>IF(COUNT(L$6:L$10,L$14:L$21,L$24:L$27,L$30:L$31)=0,"",SUM(L24:L27))</f>
         <v/>
       </c>
       <c r="M28" s="36">
-        <f>IF(COUNT(M$6:M$11,M$14:M$21,M$24:M$27,M$30:M$31)=0,"",SUM(M24:M27))</f>
+        <f>IF(COUNT(M$6:M$10,M$14:M$21,M$24:M$27,M$30:M$31)=0,"",SUM(M24:M27))</f>
         <v/>
       </c>
       <c r="N28" s="36">
@@ -3213,51 +3222,51 @@
         </is>
       </c>
       <c r="B32" s="36">
-        <f>IF(COUNT(B$6:B$11,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B30:B31))</f>
+        <f>IF(COUNT(B$6:B$10,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B30:B31))</f>
         <v>18000</v>
       </c>
       <c r="C32" s="36">
-        <f>IF(COUNT(C$6:C$11,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C30:C31))</f>
+        <f>IF(COUNT(C$6:C$10,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C30:C31))</f>
         <v>18000</v>
       </c>
       <c r="D32" s="36">
-        <f>IF(COUNT(D$6:D$11,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D30:D31))</f>
+        <f>IF(COUNT(D$6:D$10,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D30:D31))</f>
         <v>18000</v>
       </c>
       <c r="E32" s="36">
-        <f>IF(COUNT(E$6:E$11,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E30:E31))</f>
+        <f>IF(COUNT(E$6:E$10,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E30:E31))</f>
         <v>18000</v>
       </c>
       <c r="F32" s="36">
-        <f>IF(COUNT(F$6:F$11,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F30:F31))</f>
+        <f>IF(COUNT(F$6:F$10,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F30:F31))</f>
         <v>18000</v>
       </c>
       <c r="G32" s="36">
-        <f>IF(COUNT(G$6:G$11,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G30:G31))</f>
+        <f>IF(COUNT(G$6:G$10,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G30:G31))</f>
         <v>18000</v>
       </c>
       <c r="H32" s="36">
-        <f>IF(COUNT(H$6:H$11,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H30:H31))</f>
+        <f>IF(COUNT(H$6:H$10,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H30:H31))</f>
         <v>18000</v>
       </c>
       <c r="I32" s="36">
-        <f>IF(COUNT(I$6:I$11,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I30:I31))</f>
+        <f>IF(COUNT(I$6:I$10,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I30:I31))</f>
         <v>18000</v>
       </c>
       <c r="J32" s="36">
-        <f>IF(COUNT(J$6:J$11,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J30:J31))</f>
+        <f>IF(COUNT(J$6:J$10,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J30:J31))</f>
         <v/>
       </c>
       <c r="K32" s="36">
-        <f>IF(COUNT(K$6:K$11,K$14:K$21,K$24:K$27,K$30:K$31)=0,"",SUM(K30:K31))</f>
+        <f>IF(COUNT(K$6:K$10,K$14:K$21,K$24:K$27,K$30:K$31)=0,"",SUM(K30:K31))</f>
         <v/>
       </c>
       <c r="L32" s="36">
-        <f>IF(COUNT(L$6:L$11,L$14:L$21,L$24:L$27,L$30:L$31)=0,"",SUM(L30:L31))</f>
+        <f>IF(COUNT(L$6:L$10,L$14:L$21,L$24:L$27,L$30:L$31)=0,"",SUM(L30:L31))</f>
         <v/>
       </c>
       <c r="M32" s="36">
-        <f>IF(COUNT(M$6:M$11,M$14:M$21,M$24:M$27,M$30:M$31)=0,"",SUM(M30:M31))</f>
+        <f>IF(COUNT(M$6:M$10,M$14:M$21,M$24:M$27,M$30:M$31)=0,"",SUM(M30:M31))</f>
         <v/>
       </c>
       <c r="N32" s="36">
@@ -3272,291 +3281,342 @@
     <row r="33">
       <c r="A33" s="23" t="inlineStr">
         <is>
-          <t>Impostos provisionados (% da receita, Config)</t>
-        </is>
-      </c>
-      <c r="B33" s="20">
-        <f>IF(B12="","",ROUND(B12*Config!$B$7,0))</f>
-        <v>3660</v>
-      </c>
-      <c r="C33" s="20">
-        <f>IF(C12="","",ROUND(C12*Config!$B$7,0))</f>
-        <v>2727</v>
-      </c>
-      <c r="D33" s="20">
-        <f>IF(D12="","",ROUND(D12*Config!$B$7,0))</f>
-        <v>5267</v>
-      </c>
-      <c r="E33" s="20">
-        <f>IF(E12="","",ROUND(E12*Config!$B$7,0))</f>
-        <v>4355</v>
-      </c>
-      <c r="F33" s="20">
-        <f>IF(F12="","",ROUND(F12*Config!$B$7,0))</f>
-        <v>4924</v>
-      </c>
-      <c r="G33" s="20">
-        <f>IF(G12="","",ROUND(G12*Config!$B$7,0))</f>
-        <v>4824</v>
-      </c>
-      <c r="H33" s="20">
-        <f>IF(H12="","",ROUND(H12*Config!$B$7,0))</f>
-        <v>5841</v>
-      </c>
-      <c r="I33" s="20">
-        <f>IF(I12="","",ROUND(I12*Config!$B$7,0))</f>
-        <v>5537</v>
-      </c>
-      <c r="J33" s="20">
-        <f>IF(J12="","",ROUND(J12*Config!$B$7,0))</f>
-        <v/>
-      </c>
-      <c r="K33" s="20">
-        <f>IF(K12="","",ROUND(K12*Config!$B$7,0))</f>
-        <v/>
-      </c>
-      <c r="L33" s="20">
-        <f>IF(L12="","",ROUND(L12*Config!$B$7,0))</f>
-        <v/>
-      </c>
-      <c r="M33" s="20">
-        <f>IF(M12="","",ROUND(M12*Config!$B$7,0))</f>
-        <v/>
-      </c>
+          <t>Provisão de 13º e férias (planilha 10)</t>
+        </is>
+      </c>
+      <c r="B33" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="C33" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D33" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="E33" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F33" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="G33" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="H33" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="I33" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="J33" s="35" t="n"/>
+      <c r="K33" s="35" t="n"/>
+      <c r="L33" s="35" t="n"/>
+      <c r="M33" s="35" t="n"/>
       <c r="N33" s="20">
         <f>IF(COUNT(B33:M33)=0,"",SUM(B33:M33))</f>
-        <v>37135</v>
+        <v>15696</v>
       </c>
       <c r="O33" s="20">
         <f>IF(COUNT(B33:M33)=0,"",AVERAGE(B33:M33))</f>
-        <v>4641.875</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>Total de saídas (custos + variáveis + pró-labore + impostos)</t>
-        </is>
-      </c>
-      <c r="B34" s="36">
-        <f>IF(B12="","",B22+B28+B32+B33)</f>
-        <v>36230.56</v>
-      </c>
-      <c r="C34" s="36">
-        <f>IF(C12="","",C22+C28+C32+C33)</f>
-        <v>35537.28</v>
-      </c>
-      <c r="D34" s="36">
-        <f>IF(D12="","",D22+D28+D32+D33)</f>
-        <v>38605.25</v>
-      </c>
-      <c r="E34" s="36">
-        <f>IF(E12="","",E22+E28+E32+E33)</f>
-        <v>40100.7</v>
-      </c>
-      <c r="F34" s="36">
-        <f>IF(F12="","",F22+F28+F32+F33)</f>
-        <v>39993.12</v>
-      </c>
-      <c r="G34" s="36">
-        <f>IF(G12="","",G22+G28+G32+G33)</f>
-        <v>39933.91</v>
-      </c>
-      <c r="H34" s="36">
-        <f>IF(H12="","",H22+H28+H32+H33)</f>
-        <v>40502.77</v>
-      </c>
-      <c r="I34" s="36">
-        <f>IF(I12="","",I22+I28+I32+I33)</f>
-        <v>40696.12</v>
-      </c>
-      <c r="J34" s="36">
-        <f>IF(J12="","",J22+J28+J32+J33)</f>
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>Impostos provisionados (% da receita, Config)</t>
+        </is>
+      </c>
+      <c r="B34" s="20">
+        <f>IF(B11="","",ROUND(B11*Config!$B$7,0))</f>
+        <v>3660</v>
+      </c>
+      <c r="C34" s="20">
+        <f>IF(C11="","",ROUND(C11*Config!$B$7,0))</f>
+        <v>2727</v>
+      </c>
+      <c r="D34" s="20">
+        <f>IF(D11="","",ROUND(D11*Config!$B$7,0))</f>
+        <v>5316</v>
+      </c>
+      <c r="E34" s="20">
+        <f>IF(E11="","",ROUND(E11*Config!$B$7,0))</f>
+        <v>4283</v>
+      </c>
+      <c r="F34" s="20">
+        <f>IF(F11="","",ROUND(F11*Config!$B$7,0))</f>
+        <v>4922</v>
+      </c>
+      <c r="G34" s="20">
+        <f>IF(G11="","",ROUND(G11*Config!$B$7,0))</f>
+        <v>4858</v>
+      </c>
+      <c r="H34" s="20">
+        <f>IF(H11="","",ROUND(H11*Config!$B$7,0))</f>
+        <v>5881</v>
+      </c>
+      <c r="I34" s="20">
+        <f>IF(I11="","",ROUND(I11*Config!$B$7,0))</f>
+        <v>5462</v>
+      </c>
+      <c r="J34" s="20">
+        <f>IF(J11="","",ROUND(J11*Config!$B$7,0))</f>
         <v/>
       </c>
-      <c r="K34" s="36">
-        <f>IF(K12="","",K22+K28+K32+K33)</f>
+      <c r="K34" s="20">
+        <f>IF(K11="","",ROUND(K11*Config!$B$7,0))</f>
         <v/>
       </c>
-      <c r="L34" s="36">
-        <f>IF(L12="","",L22+L28+L32+L33)</f>
+      <c r="L34" s="20">
+        <f>IF(L11="","",ROUND(L11*Config!$B$7,0))</f>
         <v/>
       </c>
-      <c r="M34" s="36">
-        <f>IF(M12="","",M22+M28+M32+M33)</f>
+      <c r="M34" s="20">
+        <f>IF(M11="","",ROUND(M11*Config!$B$7,0))</f>
         <v/>
       </c>
-      <c r="N34" s="36">
+      <c r="N34" s="20">
         <f>IF(COUNT(B34:M34)=0,"",SUM(B34:M34))</f>
-        <v>311599.71</v>
-      </c>
-      <c r="O34" s="36">
+        <v>37109</v>
+      </c>
+      <c r="O34" s="20">
         <f>IF(COUNT(B34:M34)=0,"",AVERAGE(B34:M34))</f>
-        <v>38949.96375</v>
+        <v>4638.625</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>Resultado do mês (receita − saídas)</t>
+          <t>Total de saídas (custos + variáveis + pró-labore + provisões + impostos)</t>
         </is>
       </c>
       <c r="B35" s="36">
-        <f>IF(B12="","",B12-B34)</f>
-        <v>-2960.56</v>
+        <f>IF(B11="","",B22+B28+B32+N(B33)+B34)</f>
+        <v>38192.56</v>
       </c>
       <c r="C35" s="36">
-        <f>IF(C12="","",C12-C34)</f>
-        <v>-10742.28</v>
+        <f>IF(C11="","",C22+C28+C32+N(C33)+C34)</f>
+        <v>37499.28</v>
       </c>
       <c r="D35" s="36">
-        <f>IF(D12="","",D12-D34)</f>
-        <v>9274.75</v>
+        <f>IF(D11="","",D22+D28+D32+N(D33)+D34)</f>
+        <v>40616.25</v>
       </c>
       <c r="E35" s="36">
-        <f>IF(E12="","",E12-E34)</f>
-        <v>-510.699999999997</v>
+        <f>IF(E11="","",E22+E28+E32+N(E33)+E34)</f>
+        <v>41990.7</v>
       </c>
       <c r="F35" s="36">
-        <f>IF(F12="","",F12-F34)</f>
-        <v>4766.88000000001</v>
+        <f>IF(F11="","",F22+F28+F32+N(F33)+F34)</f>
+        <v>41953.12</v>
       </c>
       <c r="G35" s="36">
-        <f>IF(G12="","",G12-G34)</f>
-        <v>3921.09</v>
+        <f>IF(G11="","",G22+G28+G32+N(G33)+G34)</f>
+        <v>41929.91</v>
       </c>
       <c r="H35" s="36">
-        <f>IF(H12="","",H12-H34)</f>
-        <v>12598.23</v>
+        <f>IF(H11="","",H22+H28+H32+N(H33)+H34)</f>
+        <v>42504.77</v>
       </c>
       <c r="I35" s="36">
-        <f>IF(I12="","",I12-I34)</f>
-        <v>9639.88000000001</v>
+        <f>IF(I11="","",I22+I28+I32+N(I33)+I34)</f>
+        <v>42583.12</v>
       </c>
       <c r="J35" s="36">
-        <f>IF(J12="","",J12-J34)</f>
+        <f>IF(J11="","",J22+J28+J32+N(J33)+J34)</f>
         <v/>
       </c>
       <c r="K35" s="36">
-        <f>IF(K12="","",K12-K34)</f>
+        <f>IF(K11="","",K22+K28+K32+N(K33)+K34)</f>
         <v/>
       </c>
       <c r="L35" s="36">
-        <f>IF(L12="","",L12-L34)</f>
+        <f>IF(L11="","",L22+L28+L32+N(L33)+L34)</f>
         <v/>
       </c>
       <c r="M35" s="36">
-        <f>IF(M12="","",M12-M34)</f>
+        <f>IF(M11="","",M22+M28+M32+N(M33)+M34)</f>
         <v/>
       </c>
       <c r="N35" s="36">
         <f>IF(COUNT(B35:M35)=0,"",SUM(B35:M35))</f>
-        <v>25987.29</v>
+        <v>327269.71</v>
       </c>
       <c r="O35" s="36">
         <f>IF(COUNT(B35:M35)=0,"",AVERAGE(B35:M35))</f>
-        <v>3248.41125</v>
+        <v>40908.71375</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
+          <t>Resultado do mês (receita − saídas)</t>
+        </is>
+      </c>
+      <c r="B36" s="36">
+        <f>IF(B11="","",B11-B35)</f>
+        <v>-4922.56</v>
+      </c>
+      <c r="C36" s="36">
+        <f>IF(C11="","",C11-C35)</f>
+        <v>-12704.28</v>
+      </c>
+      <c r="D36" s="36">
+        <f>IF(D11="","",D11-D35)</f>
+        <v>7713.75</v>
+      </c>
+      <c r="E36" s="36">
+        <f>IF(E11="","",E11-E35)</f>
+        <v>-3055.7</v>
+      </c>
+      <c r="F36" s="36">
+        <f>IF(F11="","",F11-F35)</f>
+        <v>2791.88</v>
+      </c>
+      <c r="G36" s="36">
+        <f>IF(G11="","",G11-G35)</f>
+        <v>2230.09</v>
+      </c>
+      <c r="H36" s="36">
+        <f>IF(H11="","",H11-H35)</f>
+        <v>10956.23</v>
+      </c>
+      <c r="I36" s="36">
+        <f>IF(I11="","",I11-I35)</f>
+        <v>7067.88000000001</v>
+      </c>
+      <c r="J36" s="36">
+        <f>IF(J11="","",J11-J35)</f>
+        <v/>
+      </c>
+      <c r="K36" s="36">
+        <f>IF(K11="","",K11-K35)</f>
+        <v/>
+      </c>
+      <c r="L36" s="36">
+        <f>IF(L11="","",L11-L35)</f>
+        <v/>
+      </c>
+      <c r="M36" s="36">
+        <f>IF(M11="","",M11-M35)</f>
+        <v/>
+      </c>
+      <c r="N36" s="36">
+        <f>IF(COUNT(B36:M36)=0,"",SUM(B36:M36))</f>
+        <v>10077.29</v>
+      </c>
+      <c r="O36" s="36">
+        <f>IF(COUNT(B36:M36)=0,"",AVERAGE(B36:M36))</f>
+        <v>1259.66125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
           <t>Margem (resultado ÷ receita)</t>
         </is>
       </c>
-      <c r="B36" s="37">
-        <f>IF(OR(B12="",B12=0),"",B35/B12)</f>
-        <v>-0.088985873159002</v>
-      </c>
-      <c r="C36" s="37">
-        <f>IF(OR(C12="",C12=0),"",C35/C12)</f>
-        <v>-0.433243799153055</v>
-      </c>
-      <c r="D36" s="37">
-        <f>IF(OR(D12="",D12=0),"",D35/D12)</f>
-        <v>0.193708228905597</v>
-      </c>
-      <c r="E36" s="37">
-        <f>IF(OR(E12="",E12=0),"",E35/E12)</f>
-        <v>-0.0128997221520585</v>
-      </c>
-      <c r="F36" s="37">
-        <f>IF(OR(F12="",F12=0),"",F35/F12)</f>
-        <v>0.106498659517426</v>
-      </c>
-      <c r="G36" s="37">
-        <f>IF(OR(G12="",G12=0),"",G35/G12)</f>
-        <v>0.0894103294949264</v>
-      </c>
-      <c r="H36" s="37">
-        <f>IF(OR(H12="",H12=0),"",H35/H12)</f>
-        <v>0.237250334268658</v>
-      </c>
-      <c r="I36" s="37">
-        <f>IF(OR(I12="",I12=0),"",I35/I12)</f>
-        <v>0.191510648442467</v>
-      </c>
-      <c r="J36" s="37">
-        <f>IF(OR(J12="",J12=0),"",J35/J12)</f>
+      <c r="B37" s="37">
+        <f>IF(OR(B11="",B11=0),"",B36/B11)</f>
+        <v>-0.147957920048091</v>
+      </c>
+      <c r="C37" s="37">
+        <f>IF(OR(C11="",C11=0),"",C36/C11)</f>
+        <v>-0.512372655777375</v>
+      </c>
+      <c r="D37" s="37">
+        <f>IF(OR(D11="",D11=0),"",D36/D11)</f>
+        <v>0.159605834885165</v>
+      </c>
+      <c r="E37" s="37">
+        <f>IF(OR(E11="",E11=0),"",E36/E11)</f>
+        <v>-0.0784820855271606</v>
+      </c>
+      <c r="F37" s="37">
+        <f>IF(OR(F11="",F11=0),"",F36/F11)</f>
+        <v>0.0623953514359147</v>
+      </c>
+      <c r="G37" s="37">
+        <f>IF(OR(G11="",G11=0),"",G36/G11)</f>
+        <v>0.0505002264492753</v>
+      </c>
+      <c r="H37" s="37">
+        <f>IF(OR(H11="",H11=0),"",H36/H11)</f>
+        <v>0.204938740390191</v>
+      </c>
+      <c r="I37" s="37">
+        <f>IF(OR(I11="",I11=0),"",I36/I11)</f>
+        <v>0.142351211455963</v>
+      </c>
+      <c r="J37" s="37">
+        <f>IF(OR(J11="",J11=0),"",J36/J11)</f>
         <v/>
       </c>
-      <c r="K36" s="37">
-        <f>IF(OR(K12="",K12=0),"",K35/K12)</f>
+      <c r="K37" s="37">
+        <f>IF(OR(K11="",K11=0),"",K36/K11)</f>
         <v/>
       </c>
-      <c r="L36" s="37">
-        <f>IF(OR(L12="",L12=0),"",L35/L12)</f>
+      <c r="L37" s="37">
+        <f>IF(OR(L11="",L11=0),"",L36/L11)</f>
         <v/>
       </c>
-      <c r="M36" s="37">
-        <f>IF(OR(M12="",M12=0),"",M35/M12)</f>
+      <c r="M37" s="37">
+        <f>IF(OR(M11="",M11=0),"",M36/M11)</f>
         <v/>
       </c>
-      <c r="N36" s="24">
-        <f>IF(OR(N12="",N12=0),"",N35/N12)</f>
-        <v>0.0769795341645265</v>
-      </c>
-      <c r="O36" s="24">
-        <f>IF(COUNT(B36:M36)=0,"",AVERAGE(B36:M36))</f>
-        <v>0.0354061007706199</v>
-      </c>
-    </row>
-    <row r="38" ht="28" customHeight="1">
-      <c r="A38" s="38" t="inlineStr">
-        <is>
-          <t>Receita por categoria: copie de "De onde veio o dinheiro" (Painel da 09). Convênio entra quando o lote é pago (menos a glosa); cartão entra pelo bruto e a taxa vai em "Taxas de cartão". Custos e despesas: de "Para onde foi o dinheiro".</t>
-        </is>
+      <c r="N37" s="24">
+        <f>IF(OR(N11="",N11=0),"",N36/N11)</f>
+        <v>0.0298721790915586</v>
+      </c>
+      <c r="O37" s="24">
+        <f>IF(COUNT(B37:M37)=0,"",AVERAGE(B37:M37))</f>
+        <v>-0.0148776620920148</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
       <c r="A39" s="38" t="inlineStr">
         <is>
-          <t>Impostos são provisão (11 % do que entrou no mês), não a guia paga; no caixa aparece a guia do mês anterior. Retiradas extras, distribuição de lucro e despesas pessoais dos sócios não entram aqui: são movimentos sócio × clínica (planilha 11). Resultado negativo fica vermelho.</t>
+          <t>Receita por categoria: copie de "De onde veio o dinheiro" (Painel da 09). Convênio entra quando o lote é pago (menos a glosa); cartão entra pelo bruto e a taxa vai em "Taxas de cartão". Custos e despesas: de "Para onde foi o dinheiro".</t>
         </is>
       </c>
     </row>
     <row r="40" ht="28" customHeight="1">
       <c r="A40" s="38" t="inlineStr">
         <is>
+          <t>Impostos são provisão (11 % da receita do mês), não a guia paga; no caixa aparece a guia do mês anterior. A provisão de 13º e férias vem do Painel da planilha 10 (as colunas "Provisão de 13º" e "Provisão de férias" somadas): é dinheiro que o mês já deve, mesmo que só saia em dezembro e em janeiro — sem ela o resultado parece maior do que é. Retiradas extras, distribuição de lucro e despesas pessoais dos sócios não entram aqui: são movimentos sócio × clínica (planilha 11). Resultado negativo fica vermelho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="28" customHeight="1">
+      <c r="A41" s="38" t="inlineStr">
+        <is>
+          <t>Reembolsos de sócios (na 09, a categoria "Outras entradas": a devolução de uma despesa pessoal que passou pela conta da clínica) ficam numa linha própria, fora da receita: não são faturamento e não pagam imposto. Por isso a "Receita total" daqui é o "Entrou no mês" do caixa menos essa linha — a mesma base das planilhas 10 e 11.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="28" customHeight="1">
+      <c r="A42" s="38" t="inlineStr">
+        <is>
           <t>Os valores de exemplo (janeiro a agosto de 2026, meses fechados) são os totais por categoria do Painel do Caixa (09) com Pago? = Sim; setembro fica em branco porque está em andamento. O Painel da clínica (17) e o Resumo do mês (20) usam estes mesmos números.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="5">
-    <mergeCell ref="A38:O38"/>
+  <mergeCells count="6">
     <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A42:O42"/>
+    <mergeCell ref="A41:O41"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A40:O40"/>
     <mergeCell ref="A39:O39"/>
   </mergeCells>
-  <conditionalFormatting sqref="B35:O35">
+  <conditionalFormatting sqref="B36:O36">
     <cfRule type="expression" priority="1" dxfId="3">
-      <formula>AND(ISNUMBER(B35),B35&lt;0)</formula>
+      <formula>AND(ISNUMBER(B36),B36&lt;0)</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="4">
-      <formula>AND(ISNUMBER(B35),B35&gt;=0)</formula>
+      <formula>AND(ISNUMBER(B36),B36&gt;=0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:M4">
@@ -3574,7 +3634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3870,250 +3930,297 @@
     <row r="9">
       <c r="A9" s="23" t="inlineStr">
         <is>
+          <t>Provisão de 13º e férias prevista</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="K9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="L9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="M9" s="35" t="n">
+        <v>1962</v>
+      </c>
+      <c r="N9" s="20">
+        <f>IF(COUNT(B9:M9)=0,"",SUM(B9:M9))</f>
+        <v>23544</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
           <t>Impostos previstos (% da receita, Config)</t>
         </is>
       </c>
-      <c r="B9" s="20">
+      <c r="B10" s="20">
         <f>IF(B5="","",ROUND(B5*Config!$B$7,0))</f>
         <v>3960</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C10" s="20">
         <f>IF(C5="","",ROUND(C5*Config!$B$7,0))</f>
         <v>3520</v>
       </c>
-      <c r="D9" s="20">
+      <c r="D10" s="20">
         <f>IF(D5="","",ROUND(D5*Config!$B$7,0))</f>
         <v>4620</v>
       </c>
-      <c r="E9" s="20">
+      <c r="E10" s="20">
         <f>IF(E5="","",ROUND(E5*Config!$B$7,0))</f>
         <v>4620</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F10" s="20">
         <f>IF(F5="","",ROUND(F5*Config!$B$7,0))</f>
         <v>4840</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G10" s="20">
         <f>IF(G5="","",ROUND(G5*Config!$B$7,0))</f>
         <v>4840</v>
       </c>
-      <c r="H9" s="20">
+      <c r="H10" s="20">
         <f>IF(H5="","",ROUND(H5*Config!$B$7,0))</f>
         <v>5060</v>
       </c>
-      <c r="I9" s="20">
+      <c r="I10" s="20">
         <f>IF(I5="","",ROUND(I5*Config!$B$7,0))</f>
         <v>5060</v>
       </c>
-      <c r="J9" s="20">
+      <c r="J10" s="20">
         <f>IF(J5="","",ROUND(J5*Config!$B$7,0))</f>
         <v>5060</v>
       </c>
-      <c r="K9" s="20">
+      <c r="K10" s="20">
         <f>IF(K5="","",ROUND(K5*Config!$B$7,0))</f>
         <v>5060</v>
       </c>
-      <c r="L9" s="20">
+      <c r="L10" s="20">
         <f>IF(L5="","",ROUND(L5*Config!$B$7,0))</f>
         <v>4840</v>
       </c>
-      <c r="M9" s="20">
+      <c r="M10" s="20">
         <f>IF(M5="","",ROUND(M5*Config!$B$7,0))</f>
         <v>4400</v>
       </c>
-      <c r="N9" s="20">
-        <f>IF(COUNT(B9:M9)=0,"",SUM(B9:M9))</f>
-        <v>55880</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>Saídas previstas</t>
-        </is>
-      </c>
-      <c r="B10" s="20">
-        <f>IF(B5="","",N(B6)+N(B7)+N(B8)+B9)</f>
-        <v>37960</v>
-      </c>
-      <c r="C10" s="20">
-        <f>IF(C5="","",N(C6)+N(C7)+N(C8)+C9)</f>
-        <v>37520</v>
-      </c>
-      <c r="D10" s="20">
-        <f>IF(D5="","",N(D6)+N(D7)+N(D8)+D9)</f>
-        <v>38620</v>
-      </c>
-      <c r="E10" s="20">
-        <f>IF(E5="","",N(E6)+N(E7)+N(E8)+E9)</f>
-        <v>38620</v>
-      </c>
-      <c r="F10" s="20">
-        <f>IF(F5="","",N(F6)+N(F7)+N(F8)+F9)</f>
-        <v>38840</v>
-      </c>
-      <c r="G10" s="20">
-        <f>IF(G5="","",N(G6)+N(G7)+N(G8)+G9)</f>
-        <v>38840</v>
-      </c>
-      <c r="H10" s="20">
-        <f>IF(H5="","",N(H6)+N(H7)+N(H8)+H9)</f>
-        <v>39060</v>
-      </c>
-      <c r="I10" s="20">
-        <f>IF(I5="","",N(I6)+N(I7)+N(I8)+I9)</f>
-        <v>39060</v>
-      </c>
-      <c r="J10" s="20">
-        <f>IF(J5="","",N(J6)+N(J7)+N(J8)+J9)</f>
-        <v>39060</v>
-      </c>
-      <c r="K10" s="20">
-        <f>IF(K5="","",N(K6)+N(K7)+N(K8)+K9)</f>
-        <v>39060</v>
-      </c>
-      <c r="L10" s="20">
-        <f>IF(L5="","",N(L6)+N(L7)+N(L8)+L9)</f>
-        <v>38840</v>
-      </c>
-      <c r="M10" s="20">
-        <f>IF(M5="","",N(M6)+N(M7)+N(M8)+M9)</f>
-        <v>38400</v>
-      </c>
       <c r="N10" s="20">
         <f>IF(COUNT(B10:M10)=0,"",SUM(B10:M10))</f>
-        <v>463880</v>
+        <v>55880</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>Resultado previsto</t>
+          <t>Saídas previstas</t>
         </is>
       </c>
       <c r="B11" s="20">
-        <f>IF(B5="","",B5-B10)</f>
-        <v>-1960</v>
+        <f>IF(B5="","",N(B6)+N(B7)+N(B8)+N(B9)+B10)</f>
+        <v>39922</v>
       </c>
       <c r="C11" s="20">
-        <f>IF(C5="","",C5-C10)</f>
-        <v>-5520</v>
+        <f>IF(C5="","",N(C6)+N(C7)+N(C8)+N(C9)+C10)</f>
+        <v>39482</v>
       </c>
       <c r="D11" s="20">
-        <f>IF(D5="","",D5-D10)</f>
-        <v>3380</v>
+        <f>IF(D5="","",N(D6)+N(D7)+N(D8)+N(D9)+D10)</f>
+        <v>40582</v>
       </c>
       <c r="E11" s="20">
-        <f>IF(E5="","",E5-E10)</f>
-        <v>3380</v>
+        <f>IF(E5="","",N(E6)+N(E7)+N(E8)+N(E9)+E10)</f>
+        <v>40582</v>
       </c>
       <c r="F11" s="20">
-        <f>IF(F5="","",F5-F10)</f>
-        <v>5160</v>
+        <f>IF(F5="","",N(F6)+N(F7)+N(F8)+N(F9)+F10)</f>
+        <v>40802</v>
       </c>
       <c r="G11" s="20">
-        <f>IF(G5="","",G5-G10)</f>
-        <v>5160</v>
+        <f>IF(G5="","",N(G6)+N(G7)+N(G8)+N(G9)+G10)</f>
+        <v>40802</v>
       </c>
       <c r="H11" s="20">
-        <f>IF(H5="","",H5-H10)</f>
-        <v>6940</v>
+        <f>IF(H5="","",N(H6)+N(H7)+N(H8)+N(H9)+H10)</f>
+        <v>41022</v>
       </c>
       <c r="I11" s="20">
-        <f>IF(I5="","",I5-I10)</f>
-        <v>6940</v>
+        <f>IF(I5="","",N(I6)+N(I7)+N(I8)+N(I9)+I10)</f>
+        <v>41022</v>
       </c>
       <c r="J11" s="20">
-        <f>IF(J5="","",J5-J10)</f>
-        <v>6940</v>
+        <f>IF(J5="","",N(J6)+N(J7)+N(J8)+N(J9)+J10)</f>
+        <v>41022</v>
       </c>
       <c r="K11" s="20">
-        <f>IF(K5="","",K5-K10)</f>
-        <v>6940</v>
+        <f>IF(K5="","",N(K6)+N(K7)+N(K8)+N(K9)+K10)</f>
+        <v>41022</v>
       </c>
       <c r="L11" s="20">
-        <f>IF(L5="","",L5-L10)</f>
-        <v>5160</v>
+        <f>IF(L5="","",N(L6)+N(L7)+N(L8)+N(L9)+L10)</f>
+        <v>40802</v>
       </c>
       <c r="M11" s="20">
-        <f>IF(M5="","",M5-M10)</f>
-        <v>1600</v>
+        <f>IF(M5="","",N(M6)+N(M7)+N(M8)+N(M9)+M10)</f>
+        <v>40362</v>
       </c>
       <c r="N11" s="20">
         <f>IF(COUNT(B11:M11)=0,"",SUM(B11:M11))</f>
-        <v>44120</v>
+        <v>487424</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
+          <t>Resultado previsto</t>
+        </is>
+      </c>
+      <c r="B12" s="20">
+        <f>IF(B5="","",B5-B11)</f>
+        <v>-3922</v>
+      </c>
+      <c r="C12" s="20">
+        <f>IF(C5="","",C5-C11)</f>
+        <v>-7482</v>
+      </c>
+      <c r="D12" s="20">
+        <f>IF(D5="","",D5-D11)</f>
+        <v>1418</v>
+      </c>
+      <c r="E12" s="20">
+        <f>IF(E5="","",E5-E11)</f>
+        <v>1418</v>
+      </c>
+      <c r="F12" s="20">
+        <f>IF(F5="","",F5-F11)</f>
+        <v>3198</v>
+      </c>
+      <c r="G12" s="20">
+        <f>IF(G5="","",G5-G11)</f>
+        <v>3198</v>
+      </c>
+      <c r="H12" s="20">
+        <f>IF(H5="","",H5-H11)</f>
+        <v>4978</v>
+      </c>
+      <c r="I12" s="20">
+        <f>IF(I5="","",I5-I11)</f>
+        <v>4978</v>
+      </c>
+      <c r="J12" s="20">
+        <f>IF(J5="","",J5-J11)</f>
+        <v>4978</v>
+      </c>
+      <c r="K12" s="20">
+        <f>IF(K5="","",K5-K11)</f>
+        <v>4978</v>
+      </c>
+      <c r="L12" s="20">
+        <f>IF(L5="","",L5-L11)</f>
+        <v>3198</v>
+      </c>
+      <c r="M12" s="20">
+        <f>IF(M5="","",M5-M11)</f>
+        <v>-362</v>
+      </c>
+      <c r="N12" s="20">
+        <f>IF(COUNT(B12:M12)=0,"",SUM(B12:M12))</f>
+        <v>20576</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
           <t>Margem prevista</t>
         </is>
       </c>
-      <c r="B12" s="24">
-        <f>IF(OR(B5="",B5=0),"",B11/B5)</f>
-        <v>-0.0544444444444444</v>
-      </c>
-      <c r="C12" s="24">
-        <f>IF(OR(C5="",C5=0),"",C11/C5)</f>
-        <v>-0.1725</v>
-      </c>
-      <c r="D12" s="24">
-        <f>IF(OR(D5="",D5=0),"",D11/D5)</f>
-        <v>0.0804761904761905</v>
-      </c>
-      <c r="E12" s="24">
-        <f>IF(OR(E5="",E5=0),"",E11/E5)</f>
-        <v>0.0804761904761905</v>
-      </c>
-      <c r="F12" s="24">
-        <f>IF(OR(F5="",F5=0),"",F11/F5)</f>
-        <v>0.117272727272727</v>
-      </c>
-      <c r="G12" s="24">
-        <f>IF(OR(G5="",G5=0),"",G11/G5)</f>
-        <v>0.117272727272727</v>
-      </c>
-      <c r="H12" s="24">
-        <f>IF(OR(H5="",H5=0),"",H11/H5)</f>
-        <v>0.150869565217391</v>
-      </c>
-      <c r="I12" s="24">
-        <f>IF(OR(I5="",I5=0),"",I11/I5)</f>
-        <v>0.150869565217391</v>
-      </c>
-      <c r="J12" s="24">
-        <f>IF(OR(J5="",J5=0),"",J11/J5)</f>
-        <v>0.150869565217391</v>
-      </c>
-      <c r="K12" s="24">
-        <f>IF(OR(K5="",K5=0),"",K11/K5)</f>
-        <v>0.150869565217391</v>
-      </c>
-      <c r="L12" s="24">
-        <f>IF(OR(L5="",L5=0),"",L11/L5)</f>
-        <v>0.117272727272727</v>
-      </c>
-      <c r="M12" s="24">
-        <f>IF(OR(M5="",M5=0),"",M11/M5)</f>
-        <v>0.04</v>
-      </c>
-      <c r="N12" s="24">
-        <f>IF(OR(N5="",N5=0),"",N11/N5)</f>
-        <v>0.0868503937007874</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Uma boa previsão de custos fixos é a média dos últimos três meses; de receita, a produção típica da agenda (01) descontando glosa e prazo de convênio; de variáveis, repasse + materiais + taxas de cartão de um mês normal. Janeiro e julho costumam ser mais fracos.</t>
+      <c r="B13" s="24">
+        <f>IF(OR(B5="",B5=0),"",B12/B5)</f>
+        <v>-0.108944444444444</v>
+      </c>
+      <c r="C13" s="24">
+        <f>IF(OR(C5="",C5=0),"",C12/C5)</f>
+        <v>-0.2338125</v>
+      </c>
+      <c r="D13" s="24">
+        <f>IF(OR(D5="",D5=0),"",D12/D5)</f>
+        <v>0.0337619047619048</v>
+      </c>
+      <c r="E13" s="24">
+        <f>IF(OR(E5="",E5=0),"",E12/E5)</f>
+        <v>0.0337619047619048</v>
+      </c>
+      <c r="F13" s="24">
+        <f>IF(OR(F5="",F5=0),"",F12/F5)</f>
+        <v>0.0726818181818182</v>
+      </c>
+      <c r="G13" s="24">
+        <f>IF(OR(G5="",G5=0),"",G12/G5)</f>
+        <v>0.0726818181818182</v>
+      </c>
+      <c r="H13" s="24">
+        <f>IF(OR(H5="",H5=0),"",H12/H5)</f>
+        <v>0.108217391304348</v>
+      </c>
+      <c r="I13" s="24">
+        <f>IF(OR(I5="",I5=0),"",I12/I5)</f>
+        <v>0.108217391304348</v>
+      </c>
+      <c r="J13" s="24">
+        <f>IF(OR(J5="",J5=0),"",J12/J5)</f>
+        <v>0.108217391304348</v>
+      </c>
+      <c r="K13" s="24">
+        <f>IF(OR(K5="",K5=0),"",K12/K5)</f>
+        <v>0.108217391304348</v>
+      </c>
+      <c r="L13" s="24">
+        <f>IF(OR(L5="",L5=0),"",L12/L5)</f>
+        <v>0.0726818181818182</v>
+      </c>
+      <c r="M13" s="24">
+        <f>IF(OR(M5="",M5=0),"",M12/M5)</f>
+        <v>-0.00905</v>
+      </c>
+      <c r="N13" s="24">
+        <f>IF(OR(N5="",N5=0),"",N12/N5)</f>
+        <v>0.040503937007874</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Uma boa previsão de custos fixos é a média dos últimos três meses; de receita, a produção típica da agenda (01) descontando glosa e prazo de convênio; de variáveis, repasse + materiais + taxas de cartão de um mês normal; de 13º e férias, o total por mês do Painel da planilha 10. Janeiro e julho costumam ser mais fracos.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="3">
-    <mergeCell ref="A14:N14"/>
+    <mergeCell ref="A15:N15"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A1:N1"/>
   </mergeCells>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/18-resultado-mensal.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/18-resultado-mensal.xlsx
@@ -909,7 +909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1082,17 +1082,29 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar. Agenda futura e vencimentos em aberto do exemplo são relativos a hoje.</t>
+          <t>Clínica Vida Plena é uma clínica fictícia. Pacientes, convênios, nomes, contatos e valores são inventados; não há nenhum dado clínico. Apague o exemplo antes de começar.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>Data de referência</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
           <t>Suporte</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>suporte@seusociogestor.com.br · resposta em até 5 dias úteis · reembolso em até 7 dias pelo mesmo canal.</t>
         </is>
@@ -1166,22 +1178,22 @@
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="13">
         <f>IF(INDEX(Resultado!$B$11:$M$11,Config!$B$8)="","—",INDEX(Resultado!$B$11:$M$11,Config!$B$8))</f>
-        <v>49651</v>
+        <v>55841</v>
       </c>
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="13">
         <f>IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8))</f>
-        <v>42583.12</v>
+        <v>43461.61</v>
       </c>
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="14">
         <f>IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8))</f>
-        <v>7067.88000000001</v>
+        <v>12379.39</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="15">
         <f>IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8))</f>
-        <v>0.142351211455963</v>
+        <v>0.221689976898695</v>
       </c>
       <c r="H5" s="12" t="n"/>
     </row>
@@ -1240,15 +1252,15 @@
       <c r="B9" s="18" t="n"/>
       <c r="C9" s="20">
         <f>IF(INDEX(Resultado!$B$11:$M$11,Config!$B$8)="","—",INDEX(Resultado!$B$11:$M$11,Config!$B$8))</f>
-        <v>49651</v>
+        <v>55841</v>
       </c>
       <c r="D9" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$11:$M$11,Config!$B$8-1)="","—",INDEX(Resultado!$B$11:$M$11,Config!$B$8-1)))</f>
-        <v>53461</v>
+        <v>44471</v>
       </c>
       <c r="E9" s="21">
         <f>IF(OR(C9="—",D9="—",D9=0),"—",(C9-D9)/ABS(D9))</f>
-        <v>-0.0712669048465236</v>
+        <v>0.255672235839086</v>
       </c>
       <c r="F9" s="20">
         <f>IF(INDEX(Previsto!$B$5:$M$5,Config!$B$8)="","—",INDEX(Previsto!$B$5:$M$5,Config!$B$8))</f>
@@ -1256,7 +1268,7 @@
       </c>
       <c r="G9" s="21">
         <f>IF(OR(C9="—",F9="—",F9=0),"—",(C9-F9)/ABS(F9))</f>
-        <v>0.0793695652173913</v>
+        <v>0.213934782608696</v>
       </c>
       <c r="H9" s="22" t="str">
         <f>IF(OR(C9="—",F9="—"),"—",IF(C9&gt;=F9,"Dentro do previsto",IF(C9&gt;=F9*0.95,"Perto","Fora do previsto")))</f>
@@ -1304,15 +1316,15 @@
       <c r="B11" s="18" t="n"/>
       <c r="C11" s="20">
         <f>IF(INDEX(Resultado!$B$28:$M$28,Config!$B$8)="","—",INDEX(Resultado!$B$28:$M$28,Config!$B$8))</f>
-        <v>7159.12</v>
+        <v>7356.61</v>
       </c>
       <c r="D11" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$28:$M$28,Config!$B$8-1)="","—",INDEX(Resultado!$B$28:$M$28,Config!$B$8-1)))</f>
-        <v>6661.77</v>
+        <v>6366.6</v>
       </c>
       <c r="E11" s="21">
         <f>IF(OR(C11="—",D11="—",D11=0),"—",(C11-D11)/ABS(D11))</f>
-        <v>0.0746573358131547</v>
+        <v>0.155500581157918</v>
       </c>
       <c r="F11" s="20">
         <f>IF(INDEX(Previsto!$B$7:$M$7,Config!$B$8)="","—",INDEX(Previsto!$B$7:$M$7,Config!$B$8))</f>
@@ -1320,7 +1332,7 @@
       </c>
       <c r="G11" s="21">
         <f>IF(OR(C11="—",F11="—",F11=0),"—",(C11-F11)/ABS(F11))</f>
-        <v>0.193186666666667</v>
+        <v>0.226101666666667</v>
       </c>
       <c r="H11" s="22" t="str">
         <f>IF(OR(C11="—",F11="—"),"—",IF(C11&lt;=F11,"Dentro do previsto",IF(C11&lt;=F11*1.05,"Perto","Fora do previsto")))</f>
@@ -1402,15 +1414,15 @@
       <c r="B14" s="18" t="n"/>
       <c r="C14" s="20">
         <f>IF(INDEX(Resultado!$B$34:$M$34,Config!$B$8)="","—",INDEX(Resultado!$B$34:$M$34,Config!$B$8))</f>
-        <v>5462</v>
+        <v>6143</v>
       </c>
       <c r="D14" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$34:$M$34,Config!$B$8-1)="","—",INDEX(Resultado!$B$34:$M$34,Config!$B$8-1)))</f>
-        <v>5881</v>
+        <v>4892</v>
       </c>
       <c r="E14" s="21">
         <f>IF(OR(C14="—",D14="—",D14=0),"—",(C14-D14)/ABS(D14))</f>
-        <v>-0.0712463866689339</v>
+        <v>0.255723630417007</v>
       </c>
       <c r="F14" s="20">
         <f>IF(INDEX(Previsto!$B$10:$M$10,Config!$B$8)="","—",INDEX(Previsto!$B$10:$M$10,Config!$B$8))</f>
@@ -1418,7 +1430,7 @@
       </c>
       <c r="G14" s="21">
         <f>IF(OR(C14="—",F14="—",F14=0),"—",(C14-F14)/ABS(F14))</f>
-        <v>0.0794466403162055</v>
+        <v>0.21403162055336</v>
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
@@ -1435,15 +1447,15 @@
       <c r="B15" s="18" t="n"/>
       <c r="C15" s="20">
         <f>IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8))</f>
-        <v>42583.12</v>
+        <v>43461.61</v>
       </c>
       <c r="D15" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8-1)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8-1)))</f>
-        <v>42504.77</v>
+        <v>41220.6</v>
       </c>
       <c r="E15" s="21">
         <f>IF(OR(C15="—",D15="—",D15=0),"—",(C15-D15)/ABS(D15))</f>
-        <v>0.00184332252591865</v>
+        <v>0.0543662634702067</v>
       </c>
       <c r="F15" s="20">
         <f>IF(INDEX(Previsto!$B$11:$M$11,Config!$B$8)="","—",INDEX(Previsto!$B$11:$M$11,Config!$B$8))</f>
@@ -1451,11 +1463,11 @@
       </c>
       <c r="G15" s="21">
         <f>IF(OR(C15="—",F15="—",F15=0),"—",(C15-F15)/ABS(F15))</f>
-        <v>0.0380556774413728</v>
+        <v>0.0594707717809956</v>
       </c>
       <c r="H15" s="22" t="str">
         <f>IF(OR(C15="—",F15="—"),"—",IF(C15&lt;=F15,"Dentro do previsto",IF(C15&lt;=F15*1.05,"Perto","Fora do previsto")))</f>
-        <v>Perto</v>
+        <v>Fora do previsto</v>
       </c>
     </row>
     <row r="16">
@@ -1467,15 +1479,15 @@
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="20">
         <f>IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8))</f>
-        <v>7067.88000000001</v>
+        <v>12379.39</v>
       </c>
       <c r="D16" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8-1)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8-1)))</f>
-        <v>10956.23</v>
+        <v>3250.4</v>
       </c>
       <c r="E16" s="21">
         <f>IF(OR(C16="—",D16="—",D16=0),"—",(C16-D16)/ABS(D16))</f>
-        <v>-0.354898537179303</v>
+        <v>2.80857432931331</v>
       </c>
       <c r="F16" s="20">
         <f>IF(INDEX(Previsto!$B$12:$M$12,Config!$B$8)="","—",INDEX(Previsto!$B$12:$M$12,Config!$B$8))</f>
@@ -1483,7 +1495,7 @@
       </c>
       <c r="G16" s="21">
         <f>IF(OR(C16="—",F16="—",F16=0),"—",(C16-F16)/ABS(F16))</f>
-        <v>0.419823222177582</v>
+        <v>1.48682000803536</v>
       </c>
       <c r="H16" s="22" t="str">
         <f>IF(OR(C16="—",F16="—"),"—",IF(C16&gt;=F16,"Dentro do previsto",IF(C16&gt;=F16*0.95,"Perto","Fora do previsto")))</f>
@@ -1499,15 +1511,15 @@
       <c r="B17" s="18" t="n"/>
       <c r="C17" s="24">
         <f>IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8))</f>
-        <v>0.142351211455963</v>
+        <v>0.221689976898695</v>
       </c>
       <c r="D17" s="24">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8-1)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8-1)))</f>
-        <v>0.204938740390191</v>
+        <v>0.0730903285287041</v>
       </c>
       <c r="E17" s="25">
         <f>IF(OR(C17="—",D17="—"),"—",(C17-D17)*100)</f>
-        <v>-6.25875289342282</v>
+        <v>14.859964836999</v>
       </c>
       <c r="F17" s="24">
         <f>IF(INDEX(Previsto!$B$13:$M$13,Config!$B$8)="","—",INDEX(Previsto!$B$13:$M$13,Config!$B$8))</f>
@@ -1515,7 +1527,7 @@
       </c>
       <c r="G17" s="25">
         <f>IF(OR(C17="—",F17="—"),"—",(C17-F17)*100)</f>
-        <v>3.41338201516149</v>
+        <v>11.3472585594347</v>
       </c>
       <c r="H17" s="22" t="str">
         <f>IF(OR(C17="—",F17="—"),"—",IF(C17&gt;=F17,"Dentro do previsto",IF(C17&gt;=F17*0.95,"Perto","Fora do previsto")))</f>
@@ -1567,19 +1579,19 @@
       <c r="B21" s="18" t="n"/>
       <c r="C21" s="20">
         <f>IF(INDEX(Resultado!$B$6:$M$6,Config!$B$8)="","—",INDEX(Resultado!$B$6:$M$6,Config!$B$8))</f>
-        <v>33860</v>
+        <v>40050</v>
       </c>
       <c r="D21" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$6:$M$6,Config!$B$8-1)="","—",INDEX(Resultado!$B$6:$M$6,Config!$B$8-1)))</f>
-        <v>37700</v>
+        <v>28710</v>
       </c>
       <c r="E21" s="21">
         <f>IF(OR(C21="—",D21="—",D21=0),"—",(C21-D21)/ABS(D21))</f>
-        <v>-0.101856763925729</v>
+        <v>0.394984326018809</v>
       </c>
       <c r="F21" s="26">
         <f>IF(OR(C21="—",C9="—",C9=0),"—",C21/C9)</f>
-        <v>0.681960081367948</v>
+        <v>0.717214949589012</v>
       </c>
     </row>
     <row r="22">
@@ -1603,7 +1615,7 @@
       </c>
       <c r="F22" s="26">
         <f>IF(OR(C22="—",C9="—",C9=0),"—",C22/C9)</f>
-        <v>0.0932508912207206</v>
+        <v>0.0829139879300156</v>
       </c>
     </row>
     <row r="23">
@@ -1627,7 +1639,7 @@
       </c>
       <c r="F23" s="26">
         <f>IF(OR(C23="—",C9="—",C9=0),"—",C23/C9)</f>
-        <v>0.147429054802522</v>
+        <v>0.131086477677692</v>
       </c>
     </row>
     <row r="24">
@@ -1651,7 +1663,7 @@
       </c>
       <c r="F24" s="26">
         <f>IF(OR(C24="—",C9="—",C9=0),"—",C24/C9)</f>
-        <v>0.0428994380777829</v>
+        <v>0.0381440160455579</v>
       </c>
     </row>
     <row r="25">
@@ -1675,7 +1687,7 @@
       </c>
       <c r="F25" s="26">
         <f>IF(OR(C25="—",C9="—",C9=0),"—",C25/C9)</f>
-        <v>0.0344605345310266</v>
+        <v>0.0306405687577228</v>
       </c>
     </row>
     <row r="26"/>
@@ -2110,28 +2122,28 @@
         </is>
       </c>
       <c r="B6" s="35" t="n">
-        <v>25180</v>
+        <v>17220</v>
       </c>
       <c r="C6" s="35" t="n">
-        <v>15870</v>
+        <v>16725</v>
       </c>
       <c r="D6" s="35" t="n">
-        <v>37790</v>
+        <v>30000</v>
       </c>
       <c r="E6" s="35" t="n">
-        <v>28610</v>
+        <v>29830</v>
       </c>
       <c r="F6" s="35" t="n">
-        <v>27800</v>
+        <v>28435</v>
       </c>
       <c r="G6" s="35" t="n">
-        <v>28560</v>
+        <v>31640</v>
       </c>
       <c r="H6" s="35" t="n">
-        <v>37700</v>
+        <v>28710</v>
       </c>
       <c r="I6" s="35" t="n">
-        <v>33860</v>
+        <v>40050</v>
       </c>
       <c r="J6" s="35" t="n"/>
       <c r="K6" s="35" t="n"/>
@@ -2139,11 +2151,11 @@
       <c r="M6" s="35" t="n"/>
       <c r="N6" s="20">
         <f>IF(COUNT(B6:M6)=0,"",SUM(B6:M6))</f>
-        <v>235370</v>
+        <v>222610</v>
       </c>
       <c r="O6" s="20">
         <f>IF(COUNT(B6:M6)=0,"",AVERAGE(B6:M6))</f>
-        <v>29421.25</v>
+        <v>27826.25</v>
       </c>
     </row>
     <row r="7">
@@ -2326,35 +2338,35 @@
       </c>
       <c r="B11" s="36">
         <f>IF(COUNT(B$6:B$10,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B6:B10))</f>
-        <v>33270</v>
+        <v>25310</v>
       </c>
       <c r="C11" s="36">
         <f>IF(COUNT(C$6:C$10,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C6:C10))</f>
-        <v>24795</v>
+        <v>25650</v>
       </c>
       <c r="D11" s="36">
         <f>IF(COUNT(D$6:D$10,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D6:D10))</f>
-        <v>48330</v>
+        <v>40540</v>
       </c>
       <c r="E11" s="36">
         <f>IF(COUNT(E$6:E$10,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E6:E10))</f>
-        <v>38935</v>
+        <v>40155</v>
       </c>
       <c r="F11" s="36">
         <f>IF(COUNT(F$6:F$10,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F6:F10))</f>
-        <v>44745</v>
+        <v>45380</v>
       </c>
       <c r="G11" s="36">
         <f>IF(COUNT(G$6:G$10,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G6:G10))</f>
-        <v>44160</v>
+        <v>47240</v>
       </c>
       <c r="H11" s="36">
         <f>IF(COUNT(H$6:H$10,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H6:H10))</f>
-        <v>53461</v>
+        <v>44471</v>
       </c>
       <c r="I11" s="36">
         <f>IF(COUNT(I$6:I$10,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I6:I10))</f>
-        <v>49651</v>
+        <v>55841</v>
       </c>
       <c r="J11" s="36">
         <f>IF(COUNT(J$6:J$10,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J6:J10))</f>
@@ -2374,11 +2386,11 @@
       </c>
       <c r="N11" s="36">
         <f>IF(COUNT(B11:M11)=0,"",SUM(B11:M11))</f>
-        <v>337347</v>
+        <v>324587</v>
       </c>
       <c r="O11" s="36">
         <f>IF(COUNT(B11:M11)=0,"",AVERAGE(B11:M11))</f>
-        <v>42168.375</v>
+        <v>40573.375</v>
       </c>
     </row>
     <row r="12">
@@ -2923,28 +2935,28 @@
         </is>
       </c>
       <c r="B25" s="35" t="n">
-        <v>350.56</v>
+        <v>82.05</v>
       </c>
       <c r="C25" s="35" t="n">
-        <v>265.28</v>
+        <v>281.54</v>
       </c>
       <c r="D25" s="35" t="n">
-        <v>533.25</v>
+        <v>274.13</v>
       </c>
       <c r="E25" s="35" t="n">
-        <v>435.7</v>
+        <v>485.1</v>
       </c>
       <c r="F25" s="35" t="n">
-        <v>464.12</v>
+        <v>478.29</v>
       </c>
       <c r="G25" s="35" t="n">
-        <v>354.91</v>
+        <v>455.87</v>
       </c>
       <c r="H25" s="35" t="n">
-        <v>641.77</v>
+        <v>346.6</v>
       </c>
       <c r="I25" s="35" t="n">
-        <v>484.12</v>
+        <v>681.61</v>
       </c>
       <c r="J25" s="35" t="n"/>
       <c r="K25" s="35" t="n"/>
@@ -2952,11 +2964,11 @@
       <c r="M25" s="35" t="n"/>
       <c r="N25" s="20">
         <f>IF(COUNT(B25:M25)=0,"",SUM(B25:M25))</f>
-        <v>3529.71</v>
+        <v>3085.19</v>
       </c>
       <c r="O25" s="20">
         <f>IF(COUNT(B25:M25)=0,"",AVERAGE(B25:M25))</f>
-        <v>441.21375</v>
+        <v>385.64875</v>
       </c>
     </row>
     <row r="26">
@@ -3053,35 +3065,35 @@
       </c>
       <c r="B28" s="36">
         <f>IF(COUNT(B$6:B$10,B$14:B$21,B$24:B$27,B$30:B$31)=0,"",SUM(B24:B27))</f>
-        <v>4570.56</v>
+        <v>4302.05</v>
       </c>
       <c r="C28" s="36">
         <f>IF(COUNT(C$6:C$10,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C24:C27))</f>
-        <v>4810.28</v>
+        <v>4826.54</v>
       </c>
       <c r="D28" s="36">
         <f>IF(COUNT(D$6:D$10,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D24:D27))</f>
-        <v>5338.25</v>
+        <v>5079.13</v>
       </c>
       <c r="E28" s="36">
         <f>IF(COUNT(E$6:E$10,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E24:E27))</f>
-        <v>7745.7</v>
+        <v>7795.1</v>
       </c>
       <c r="F28" s="36">
         <f>IF(COUNT(F$6:F$10,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F24:F27))</f>
-        <v>7069.12</v>
+        <v>7083.29</v>
       </c>
       <c r="G28" s="36">
         <f>IF(COUNT(G$6:G$10,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G24:G27))</f>
-        <v>7109.91</v>
+        <v>7210.87</v>
       </c>
       <c r="H28" s="36">
         <f>IF(COUNT(H$6:H$10,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H24:H27))</f>
-        <v>6661.77</v>
+        <v>6366.6</v>
       </c>
       <c r="I28" s="36">
         <f>IF(COUNT(I$6:I$10,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I24:I27))</f>
-        <v>7159.12</v>
+        <v>7356.61</v>
       </c>
       <c r="J28" s="36">
         <f>IF(COUNT(J$6:J$10,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J24:J27))</f>
@@ -3101,11 +3113,11 @@
       </c>
       <c r="N28" s="36">
         <f>IF(COUNT(B28:M28)=0,"",SUM(B28:M28))</f>
-        <v>50464.71</v>
+        <v>50020.19</v>
       </c>
       <c r="O28" s="36">
         <f>IF(COUNT(B28:M28)=0,"",AVERAGE(B28:M28))</f>
-        <v>6308.08875</v>
+        <v>6252.52375</v>
       </c>
     </row>
     <row r="29">
@@ -3329,35 +3341,35 @@
       </c>
       <c r="B34" s="20">
         <f>IF(B11="","",ROUND(B11*Config!$B$7,0))</f>
-        <v>3660</v>
+        <v>2784</v>
       </c>
       <c r="C34" s="20">
         <f>IF(C11="","",ROUND(C11*Config!$B$7,0))</f>
-        <v>2727</v>
+        <v>2822</v>
       </c>
       <c r="D34" s="20">
         <f>IF(D11="","",ROUND(D11*Config!$B$7,0))</f>
-        <v>5316</v>
+        <v>4459</v>
       </c>
       <c r="E34" s="20">
         <f>IF(E11="","",ROUND(E11*Config!$B$7,0))</f>
-        <v>4283</v>
+        <v>4417</v>
       </c>
       <c r="F34" s="20">
         <f>IF(F11="","",ROUND(F11*Config!$B$7,0))</f>
-        <v>4922</v>
+        <v>4992</v>
       </c>
       <c r="G34" s="20">
         <f>IF(G11="","",ROUND(G11*Config!$B$7,0))</f>
-        <v>4858</v>
+        <v>5196</v>
       </c>
       <c r="H34" s="20">
         <f>IF(H11="","",ROUND(H11*Config!$B$7,0))</f>
-        <v>5881</v>
+        <v>4892</v>
       </c>
       <c r="I34" s="20">
         <f>IF(I11="","",ROUND(I11*Config!$B$7,0))</f>
-        <v>5462</v>
+        <v>6143</v>
       </c>
       <c r="J34" s="20">
         <f>IF(J11="","",ROUND(J11*Config!$B$7,0))</f>
@@ -3377,11 +3389,11 @@
       </c>
       <c r="N34" s="20">
         <f>IF(COUNT(B34:M34)=0,"",SUM(B34:M34))</f>
-        <v>37109</v>
+        <v>35705</v>
       </c>
       <c r="O34" s="20">
         <f>IF(COUNT(B34:M34)=0,"",AVERAGE(B34:M34))</f>
-        <v>4638.625</v>
+        <v>4463.125</v>
       </c>
     </row>
     <row r="35">
@@ -3392,35 +3404,35 @@
       </c>
       <c r="B35" s="36">
         <f>IF(B11="","",B22+B28+B32+N(B33)+B34)</f>
-        <v>38192.56</v>
+        <v>37048.05</v>
       </c>
       <c r="C35" s="36">
         <f>IF(C11="","",C22+C28+C32+N(C33)+C34)</f>
-        <v>37499.28</v>
+        <v>37610.54</v>
       </c>
       <c r="D35" s="36">
         <f>IF(D11="","",D22+D28+D32+N(D33)+D34)</f>
-        <v>40616.25</v>
+        <v>39500.13</v>
       </c>
       <c r="E35" s="36">
         <f>IF(E11="","",E22+E28+E32+N(E33)+E34)</f>
-        <v>41990.7</v>
+        <v>42174.1</v>
       </c>
       <c r="F35" s="36">
         <f>IF(F11="","",F22+F28+F32+N(F33)+F34)</f>
-        <v>41953.12</v>
+        <v>42037.29</v>
       </c>
       <c r="G35" s="36">
         <f>IF(G11="","",G22+G28+G32+N(G33)+G34)</f>
-        <v>41929.91</v>
+        <v>42368.87</v>
       </c>
       <c r="H35" s="36">
         <f>IF(H11="","",H22+H28+H32+N(H33)+H34)</f>
-        <v>42504.77</v>
+        <v>41220.6</v>
       </c>
       <c r="I35" s="36">
         <f>IF(I11="","",I22+I28+I32+N(I33)+I34)</f>
-        <v>42583.12</v>
+        <v>43461.61</v>
       </c>
       <c r="J35" s="36">
         <f>IF(J11="","",J22+J28+J32+N(J33)+J34)</f>
@@ -3440,11 +3452,11 @@
       </c>
       <c r="N35" s="36">
         <f>IF(COUNT(B35:M35)=0,"",SUM(B35:M35))</f>
-        <v>327269.71</v>
+        <v>325421.19</v>
       </c>
       <c r="O35" s="36">
         <f>IF(COUNT(B35:M35)=0,"",AVERAGE(B35:M35))</f>
-        <v>40908.71375</v>
+        <v>40677.64875</v>
       </c>
     </row>
     <row r="36">
@@ -3455,35 +3467,35 @@
       </c>
       <c r="B36" s="36">
         <f>IF(B11="","",B11-B35)</f>
-        <v>-4922.56</v>
+        <v>-11738.05</v>
       </c>
       <c r="C36" s="36">
         <f>IF(C11="","",C11-C35)</f>
-        <v>-12704.28</v>
+        <v>-11960.54</v>
       </c>
       <c r="D36" s="36">
         <f>IF(D11="","",D11-D35)</f>
-        <v>7713.75</v>
+        <v>1039.87</v>
       </c>
       <c r="E36" s="36">
         <f>IF(E11="","",E11-E35)</f>
-        <v>-3055.7</v>
+        <v>-2019.1</v>
       </c>
       <c r="F36" s="36">
         <f>IF(F11="","",F11-F35)</f>
-        <v>2791.88</v>
+        <v>3342.71</v>
       </c>
       <c r="G36" s="36">
         <f>IF(G11="","",G11-G35)</f>
-        <v>2230.09</v>
+        <v>4871.13000000001</v>
       </c>
       <c r="H36" s="36">
         <f>IF(H11="","",H11-H35)</f>
-        <v>10956.23</v>
+        <v>3250.4</v>
       </c>
       <c r="I36" s="36">
         <f>IF(I11="","",I11-I35)</f>
-        <v>7067.88000000001</v>
+        <v>12379.39</v>
       </c>
       <c r="J36" s="36">
         <f>IF(J11="","",J11-J35)</f>
@@ -3503,11 +3515,11 @@
       </c>
       <c r="N36" s="36">
         <f>IF(COUNT(B36:M36)=0,"",SUM(B36:M36))</f>
-        <v>10077.29</v>
+        <v>-834.190000000002</v>
       </c>
       <c r="O36" s="36">
         <f>IF(COUNT(B36:M36)=0,"",AVERAGE(B36:M36))</f>
-        <v>1259.66125</v>
+        <v>-104.27375</v>
       </c>
     </row>
     <row r="37">
@@ -3518,35 +3530,35 @@
       </c>
       <c r="B37" s="37">
         <f>IF(OR(B11="",B11=0),"",B36/B11)</f>
-        <v>-0.147957920048091</v>
+        <v>-0.46377123666535</v>
       </c>
       <c r="C37" s="37">
         <f>IF(OR(C11="",C11=0),"",C36/C11)</f>
-        <v>-0.512372655777375</v>
+        <v>-0.466297855750487</v>
       </c>
       <c r="D37" s="37">
         <f>IF(OR(D11="",D11=0),"",D36/D11)</f>
-        <v>0.159605834885165</v>
+        <v>0.0256504686729155</v>
       </c>
       <c r="E37" s="37">
         <f>IF(OR(E11="",E11=0),"",E36/E11)</f>
-        <v>-0.0784820855271606</v>
+        <v>-0.0502826547129871</v>
       </c>
       <c r="F37" s="37">
         <f>IF(OR(F11="",F11=0),"",F36/F11)</f>
-        <v>0.0623953514359147</v>
+        <v>0.0736604230938739</v>
       </c>
       <c r="G37" s="37">
         <f>IF(OR(G11="",G11=0),"",G36/G11)</f>
-        <v>0.0505002264492753</v>
+        <v>0.103114521591871</v>
       </c>
       <c r="H37" s="37">
         <f>IF(OR(H11="",H11=0),"",H36/H11)</f>
-        <v>0.204938740390191</v>
+        <v>0.0730903285287041</v>
       </c>
       <c r="I37" s="37">
         <f>IF(OR(I11="",I11=0),"",I36/I11)</f>
-        <v>0.142351211455963</v>
+        <v>0.221689976898695</v>
       </c>
       <c r="J37" s="37">
         <f>IF(OR(J11="",J11=0),"",J36/J11)</f>
@@ -3566,11 +3578,11 @@
       </c>
       <c r="N37" s="24">
         <f>IF(OR(N11="",N11=0),"",N36/N11)</f>
-        <v>0.0298721790915586</v>
+        <v>-0.00257000434398174</v>
       </c>
       <c r="O37" s="24">
         <f>IF(COUNT(B37:M37)=0,"",AVERAGE(B37:M37))</f>
-        <v>-0.0148776620920148</v>
+        <v>-0.0603932535428456</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/18-resultado-mensal.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/18-resultado-mensal.xlsx
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores e gráficos funcionam.</t>
+          <t>Faça upload no Google Drive e abra com o Google Sheets. Fórmulas, listas, cores, semáforos e gráficos funcionam: as regras de cor que dependem do mês escolhido em Config usam INDIRECT, que é a forma que o Sheets aceita para regra condicional apontar para outra aba.</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os seus dados, troque a data de referência em Config por =HOJE(): daí em diante ela acompanha o dia.</t>
+          <t>O exemplo está congelado em 14/09/2026, para todos os arquivos do kit mostrarem a mesma foto e os números fecharem entre eles. Ao começar a usar com os SEUS dados, troque em Config: a data de referência por =HOJE(), o ano, o mês do painel, o trimestre (onde houver) e a lista de feriados. Trocar só a data de referência deixa o resto apontando para 2026.</t>
         </is>
       </c>
     </row>
@@ -3633,7 +3633,7 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:M4">
     <cfRule type="expression" priority="3" dxfId="5">
-      <formula>COLUMN()-1=Config!$B$8</formula>
+      <formula>COLUMN()-1=INDIRECT("Config!$B$8")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/18-resultado-mensal.xlsx
+++ b/projetos/gestao-ia-planilhas/produto/kit-medicos/entrega/18-resultado-mensal.xlsx
@@ -1183,17 +1183,17 @@
       <c r="B5" s="8" t="n"/>
       <c r="C5" s="13">
         <f>IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8))</f>
-        <v>43461.61</v>
+        <v>43461.6</v>
       </c>
       <c r="D5" s="8" t="n"/>
       <c r="E5" s="14">
         <f>IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8))</f>
-        <v>12379.39</v>
+        <v>12379.4</v>
       </c>
       <c r="F5" s="10" t="n"/>
       <c r="G5" s="15">
         <f>IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8))</f>
-        <v>0.221689976898695</v>
+        <v>0.221690155978582</v>
       </c>
       <c r="H5" s="12" t="n"/>
     </row>
@@ -1316,15 +1316,15 @@
       <c r="B11" s="18" t="n"/>
       <c r="C11" s="20">
         <f>IF(INDEX(Resultado!$B$28:$M$28,Config!$B$8)="","—",INDEX(Resultado!$B$28:$M$28,Config!$B$8))</f>
-        <v>7356.61</v>
+        <v>7356.6</v>
       </c>
       <c r="D11" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$28:$M$28,Config!$B$8-1)="","—",INDEX(Resultado!$B$28:$M$28,Config!$B$8-1)))</f>
-        <v>6366.6</v>
+        <v>6366.61</v>
       </c>
       <c r="E11" s="21">
         <f>IF(OR(C11="—",D11="—",D11=0),"—",(C11-D11)/ABS(D11))</f>
-        <v>0.155500581157918</v>
+        <v>0.155497195524777</v>
       </c>
       <c r="F11" s="20">
         <f>IF(INDEX(Previsto!$B$7:$M$7,Config!$B$8)="","—",INDEX(Previsto!$B$7:$M$7,Config!$B$8))</f>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="G11" s="21">
         <f>IF(OR(C11="—",F11="—",F11=0),"—",(C11-F11)/ABS(F11))</f>
-        <v>0.226101666666667</v>
+        <v>0.2261</v>
       </c>
       <c r="H11" s="22" t="str">
         <f>IF(OR(C11="—",F11="—"),"—",IF(C11&lt;=F11,"Dentro do previsto",IF(C11&lt;=F11*1.05,"Perto","Fora do previsto")))</f>
@@ -1447,15 +1447,15 @@
       <c r="B15" s="18" t="n"/>
       <c r="C15" s="20">
         <f>IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8))</f>
-        <v>43461.61</v>
+        <v>43461.6</v>
       </c>
       <c r="D15" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$35:$M$35,Config!$B$8-1)="","—",INDEX(Resultado!$B$35:$M$35,Config!$B$8-1)))</f>
-        <v>41220.6</v>
+        <v>41220.61</v>
       </c>
       <c r="E15" s="21">
         <f>IF(OR(C15="—",D15="—",D15=0),"—",(C15-D15)/ABS(D15))</f>
-        <v>0.0543662634702067</v>
+        <v>0.054365765086931</v>
       </c>
       <c r="F15" s="20">
         <f>IF(INDEX(Previsto!$B$11:$M$11,Config!$B$8)="","—",INDEX(Previsto!$B$11:$M$11,Config!$B$8))</f>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="G15" s="21">
         <f>IF(OR(C15="—",F15="—",F15=0),"—",(C15-F15)/ABS(F15))</f>
-        <v>0.0594707717809956</v>
+        <v>0.0594705280093608</v>
       </c>
       <c r="H15" s="22" t="str">
         <f>IF(OR(C15="—",F15="—"),"—",IF(C15&lt;=F15,"Dentro do previsto",IF(C15&lt;=F15*1.05,"Perto","Fora do previsto")))</f>
@@ -1479,15 +1479,15 @@
       <c r="B16" s="18" t="n"/>
       <c r="C16" s="20">
         <f>IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8))</f>
-        <v>12379.39</v>
+        <v>12379.4</v>
       </c>
       <c r="D16" s="20">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$36:$M$36,Config!$B$8-1)="","—",INDEX(Resultado!$B$36:$M$36,Config!$B$8-1)))</f>
-        <v>3250.4</v>
+        <v>3250.39</v>
       </c>
       <c r="E16" s="21">
         <f>IF(OR(C16="—",D16="—",D16=0),"—",(C16-D16)/ABS(D16))</f>
-        <v>2.80857432931331</v>
+        <v>2.80858912315138</v>
       </c>
       <c r="F16" s="20">
         <f>IF(INDEX(Previsto!$B$12:$M$12,Config!$B$8)="","—",INDEX(Previsto!$B$12:$M$12,Config!$B$8))</f>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G16" s="21">
         <f>IF(OR(C16="—",F16="—",F16=0),"—",(C16-F16)/ABS(F16))</f>
-        <v>1.48682000803536</v>
+        <v>1.48682201687425</v>
       </c>
       <c r="H16" s="22" t="str">
         <f>IF(OR(C16="—",F16="—"),"—",IF(C16&gt;=F16,"Dentro do previsto",IF(C16&gt;=F16*0.95,"Perto","Fora do previsto")))</f>
@@ -1511,15 +1511,15 @@
       <c r="B17" s="18" t="n"/>
       <c r="C17" s="24">
         <f>IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8))</f>
-        <v>0.221689976898695</v>
+        <v>0.221690155978582</v>
       </c>
       <c r="D17" s="24">
         <f>IF(Config!$B$8&lt;=1,"—",IF(INDEX(Resultado!$B$37:$M$37,Config!$B$8-1)="","—",INDEX(Resultado!$B$37:$M$37,Config!$B$8-1)))</f>
-        <v>0.0730903285287041</v>
+        <v>0.0730901036630613</v>
       </c>
       <c r="E17" s="25">
         <f>IF(OR(C17="—",D17="—"),"—",(C17-D17)*100)</f>
-        <v>14.859964836999</v>
+        <v>14.8600052315521</v>
       </c>
       <c r="F17" s="24">
         <f>IF(INDEX(Previsto!$B$13:$M$13,Config!$B$8)="","—",INDEX(Previsto!$B$13:$M$13,Config!$B$8))</f>
@@ -1527,7 +1527,7 @@
       </c>
       <c r="G17" s="25">
         <f>IF(OR(C17="—",F17="—"),"—",(C17-F17)*100)</f>
-        <v>11.3472585594347</v>
+        <v>11.3472764674234</v>
       </c>
       <c r="H17" s="22" t="str">
         <f>IF(OR(C17="—",F17="—"),"—",IF(C17&gt;=F17,"Dentro do previsto",IF(C17&gt;=F17*0.95,"Perto","Fora do previsto")))</f>
@@ -2938,25 +2938,25 @@
         <v>82.05</v>
       </c>
       <c r="C25" s="35" t="n">
-        <v>281.54</v>
+        <v>281.55</v>
       </c>
       <c r="D25" s="35" t="n">
         <v>274.13</v>
       </c>
       <c r="E25" s="35" t="n">
-        <v>485.1</v>
+        <v>485.11</v>
       </c>
       <c r="F25" s="35" t="n">
-        <v>478.29</v>
+        <v>478.27</v>
       </c>
       <c r="G25" s="35" t="n">
         <v>455.87</v>
       </c>
       <c r="H25" s="35" t="n">
-        <v>346.6</v>
+        <v>346.61</v>
       </c>
       <c r="I25" s="35" t="n">
-        <v>681.61</v>
+        <v>681.6</v>
       </c>
       <c r="J25" s="35" t="n"/>
       <c r="K25" s="35" t="n"/>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C28" s="36">
         <f>IF(COUNT(C$6:C$10,C$14:C$21,C$24:C$27,C$30:C$31)=0,"",SUM(C24:C27))</f>
-        <v>4826.54</v>
+        <v>4826.55</v>
       </c>
       <c r="D28" s="36">
         <f>IF(COUNT(D$6:D$10,D$14:D$21,D$24:D$27,D$30:D$31)=0,"",SUM(D24:D27))</f>
@@ -3077,11 +3077,11 @@
       </c>
       <c r="E28" s="36">
         <f>IF(COUNT(E$6:E$10,E$14:E$21,E$24:E$27,E$30:E$31)=0,"",SUM(E24:E27))</f>
-        <v>7795.1</v>
+        <v>7795.11</v>
       </c>
       <c r="F28" s="36">
         <f>IF(COUNT(F$6:F$10,F$14:F$21,F$24:F$27,F$30:F$31)=0,"",SUM(F24:F27))</f>
-        <v>7083.29</v>
+        <v>7083.27</v>
       </c>
       <c r="G28" s="36">
         <f>IF(COUNT(G$6:G$10,G$14:G$21,G$24:G$27,G$30:G$31)=0,"",SUM(G24:G27))</f>
@@ -3089,11 +3089,11 @@
       </c>
       <c r="H28" s="36">
         <f>IF(COUNT(H$6:H$10,H$14:H$21,H$24:H$27,H$30:H$31)=0,"",SUM(H24:H27))</f>
-        <v>6366.6</v>
+        <v>6366.61</v>
       </c>
       <c r="I28" s="36">
         <f>IF(COUNT(I$6:I$10,I$14:I$21,I$24:I$27,I$30:I$31)=0,"",SUM(I24:I27))</f>
-        <v>7356.61</v>
+        <v>7356.6</v>
       </c>
       <c r="J28" s="36">
         <f>IF(COUNT(J$6:J$10,J$14:J$21,J$24:J$27,J$30:J$31)=0,"",SUM(J24:J27))</f>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="C35" s="36">
         <f>IF(C11="","",C22+C28+C32+N(C33)+C34)</f>
-        <v>37610.54</v>
+        <v>37610.55</v>
       </c>
       <c r="D35" s="36">
         <f>IF(D11="","",D22+D28+D32+N(D33)+D34)</f>
@@ -3416,11 +3416,11 @@
       </c>
       <c r="E35" s="36">
         <f>IF(E11="","",E22+E28+E32+N(E33)+E34)</f>
-        <v>42174.1</v>
+        <v>42174.11</v>
       </c>
       <c r="F35" s="36">
         <f>IF(F11="","",F22+F28+F32+N(F33)+F34)</f>
-        <v>42037.29</v>
+        <v>42037.27</v>
       </c>
       <c r="G35" s="36">
         <f>IF(G11="","",G22+G28+G32+N(G33)+G34)</f>
@@ -3428,11 +3428,11 @@
       </c>
       <c r="H35" s="36">
         <f>IF(H11="","",H22+H28+H32+N(H33)+H34)</f>
-        <v>41220.6</v>
+        <v>41220.61</v>
       </c>
       <c r="I35" s="36">
         <f>IF(I11="","",I22+I28+I32+N(I33)+I34)</f>
-        <v>43461.61</v>
+        <v>43461.6</v>
       </c>
       <c r="J35" s="36">
         <f>IF(J11="","",J22+J28+J32+N(J33)+J34)</f>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C36" s="36">
         <f>IF(C11="","",C11-C35)</f>
-        <v>-11960.54</v>
+        <v>-11960.55</v>
       </c>
       <c r="D36" s="36">
         <f>IF(D11="","",D11-D35)</f>
@@ -3479,11 +3479,11 @@
       </c>
       <c r="E36" s="36">
         <f>IF(E11="","",E11-E35)</f>
-        <v>-2019.1</v>
+        <v>-2019.11</v>
       </c>
       <c r="F36" s="36">
         <f>IF(F11="","",F11-F35)</f>
-        <v>3342.71</v>
+        <v>3342.73</v>
       </c>
       <c r="G36" s="36">
         <f>IF(G11="","",G11-G35)</f>
@@ -3491,11 +3491,11 @@
       </c>
       <c r="H36" s="36">
         <f>IF(H11="","",H11-H35)</f>
-        <v>3250.4</v>
+        <v>3250.39</v>
       </c>
       <c r="I36" s="36">
         <f>IF(I11="","",I11-I35)</f>
-        <v>12379.39</v>
+        <v>12379.4</v>
       </c>
       <c r="J36" s="36">
         <f>IF(J11="","",J11-J35)</f>
@@ -3515,11 +3515,11 @@
       </c>
       <c r="N36" s="36">
         <f>IF(COUNT(B36:M36)=0,"",SUM(B36:M36))</f>
-        <v>-834.190000000002</v>
+        <v>-834.19000000001</v>
       </c>
       <c r="O36" s="36">
         <f>IF(COUNT(B36:M36)=0,"",AVERAGE(B36:M36))</f>
-        <v>-104.27375</v>
+        <v>-104.273750000001</v>
       </c>
     </row>
     <row r="37">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C37" s="37">
         <f>IF(OR(C11="",C11=0),"",C36/C11)</f>
-        <v>-0.466297855750487</v>
+        <v>-0.466298245614035</v>
       </c>
       <c r="D37" s="37">
         <f>IF(OR(D11="",D11=0),"",D36/D11)</f>
@@ -3542,11 +3542,11 @@
       </c>
       <c r="E37" s="37">
         <f>IF(OR(E11="",E11=0),"",E36/E11)</f>
-        <v>-0.0502826547129871</v>
+        <v>-0.0502829037479766</v>
       </c>
       <c r="F37" s="37">
         <f>IF(OR(F11="",F11=0),"",F36/F11)</f>
-        <v>0.0736604230938739</v>
+        <v>0.0736608638166592</v>
       </c>
       <c r="G37" s="37">
         <f>IF(OR(G11="",G11=0),"",G36/G11)</f>
@@ -3554,11 +3554,11 @@
       </c>
       <c r="H37" s="37">
         <f>IF(OR(H11="",H11=0),"",H36/H11)</f>
-        <v>0.0730903285287041</v>
+        <v>0.0730901036630613</v>
       </c>
       <c r="I37" s="37">
         <f>IF(OR(I11="",I11=0),"",I36/I11)</f>
-        <v>0.221689976898695</v>
+        <v>0.221690155978582</v>
       </c>
       <c r="J37" s="37">
         <f>IF(OR(J11="",J11=0),"",J36/J11)</f>
@@ -3578,11 +3578,11 @@
       </c>
       <c r="N37" s="24">
         <f>IF(OR(N11="",N11=0),"",N36/N11)</f>
-        <v>-0.00257000434398174</v>
+        <v>-0.00257000434398177</v>
       </c>
       <c r="O37" s="24">
         <f>IF(COUNT(B37:M37)=0,"",AVERAGE(B37:M37))</f>
-        <v>-0.0603932535428456</v>
+        <v>-0.060393284038034</v>
       </c>
     </row>
     <row r="39" ht="28" customHeight="1">
